--- a/knowledge/data/DANH SÁCH BÍ THƯ, TRƯỞNG KHU PHỐ PHƯỜNG TÂN HƯNG MỚI (1).xlsx
+++ b/knowledge/data/DANH SÁCH BÍ THƯ, TRƯỞNG KHU PHỐ PHƯỜNG TÂN HƯNG MỚI (1).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\X\Documents\Zalo Received Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\vn_testing\backend\knowledge\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5B9C480-2AD1-4BEC-8CE8-0B9896E79818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18679103-21AB-45AB-BAE6-47B09CC04645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{7661DE85-3A2C-4118-BFA6-14A974D2AA07}"/>
+    <workbookView xWindow="1080" yWindow="1080" windowWidth="21600" windowHeight="11295" xr2:uid="{7661DE85-3A2C-4118-BFA6-14A974D2AA07}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="397">
   <si>
     <t>Họ và tên</t>
   </si>
@@ -1248,10 +1248,6 @@
     <t>DANH SÁCH BÍ THƯ, TRƯỞNG KHU PHỐ PHƯỜNG TÂN HƯNG - SAU SẮP XẾP VÀ ĐỔI TÊN KHU PHỐ</t>
   </si>
   <si>
-    <t>Tên Khu phố
-P. Tân Hưng</t>
-  </si>
-  <si>
     <t>Điện thoại</t>
   </si>
   <si>
@@ -1262,304 +1258,8 @@
 0915796464</t>
   </si>
   <si>
-    <t>Khu phố 13
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 15
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 18
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 16
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 14
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 17
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 1
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 12
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 2
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 3
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 4
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 5
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 8
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 6
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 7
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 9
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 10
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 11
--Tân Kiểng</t>
-  </si>
-  <si>
-    <t>Khu phố 11
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 12
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 13
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 15
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 14
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 10
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 9
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 8
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 7
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 6
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 5
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 4
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 3
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 2
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 1
--Tân Quy</t>
-  </si>
-  <si>
-    <t>Khu phố 2
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 1
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 19
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 18
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 17
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 16
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 3
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 4
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 5
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 6
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 7
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 8
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 9
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 10
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 11
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 12
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 13
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 14
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 15
--Tân Phong</t>
-  </si>
-  <si>
-    <t>Khu phố 4
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 5
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 6
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 22
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 21
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 23
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 7
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 8
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 9
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 19
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 20
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 3
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 2
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 1
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 16
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 15
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 14
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 17
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 18
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 10
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 11
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 13
--Tân Hưng</t>
-  </si>
-  <si>
-    <t>Khu phố 12
--Tân Hưng</t>
+    <t>Tên Khu phố
+P. Tân Hưng mới</t>
   </si>
 </sst>
 </file>
@@ -1891,38 +1591,38 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1948,9 +1648,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1988,7 +1688,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2094,7 +1794,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2236,7 +1936,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2245,49 +1945,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4233DBD-70BF-498C-AA89-0E46014232DF}">
   <dimension ref="A1:K149"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="16.5546875" style="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="16.5703125" style="16" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="29" style="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="41.21875" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="5" max="5" width="41.28515625" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="60" t="s">
         <v>391</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
+      <c r="B1" s="61"/>
+      <c r="C1" s="61"/>
       <c r="D1" s="15"/>
-      <c r="E1" s="66" t="s">
+      <c r="E1" s="62" t="s">
         <v>390</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="63" t="s">
         <v>392</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
-      <c r="F3" s="67"/>
-      <c r="G3" s="67"/>
-    </row>
-    <row r="5" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="63"/>
+    </row>
+    <row r="5" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>109</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>0</v>
@@ -2296,20 +1996,18 @@
         <v>1</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" ht="37.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>1</v>
       </c>
-      <c r="B6" s="58" t="s">
-        <v>397</v>
-      </c>
-      <c r="C6" s="57" t="s">
+      <c r="B6" s="57"/>
+      <c r="C6" s="59" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="48" t="s">
@@ -2323,12 +2021,12 @@
       </c>
       <c r="G6" s="21"/>
     </row>
-    <row r="7" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="59"/>
-      <c r="C7" s="57"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="59"/>
       <c r="D7" s="49" t="s">
         <v>29</v>
       </c>
@@ -2340,14 +2038,12 @@
       </c>
       <c r="G7" s="24"/>
     </row>
-    <row r="8" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
         <v>3</v>
       </c>
-      <c r="B8" s="58" t="s">
-        <v>398</v>
-      </c>
-      <c r="C8" s="57" t="s">
+      <c r="B8" s="57"/>
+      <c r="C8" s="59" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="48" t="s">
@@ -2361,12 +2057,12 @@
       </c>
       <c r="G8" s="21"/>
     </row>
-    <row r="9" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="59"/>
-      <c r="C9" s="57"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="59"/>
       <c r="D9" s="49" t="s">
         <v>35</v>
       </c>
@@ -2378,14 +2074,12 @@
       </c>
       <c r="G9" s="24"/>
     </row>
-    <row r="10" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A10" s="9">
         <v>5</v>
       </c>
-      <c r="B10" s="58" t="s">
-        <v>399</v>
-      </c>
-      <c r="C10" s="57" t="s">
+      <c r="B10" s="57"/>
+      <c r="C10" s="59" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="48" t="s">
@@ -2399,12 +2093,12 @@
       </c>
       <c r="G10" s="21"/>
     </row>
-    <row r="11" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A11" s="9">
         <v>6</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="57"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="59"/>
       <c r="D11" s="49" t="s">
         <v>40</v>
       </c>
@@ -2416,14 +2110,12 @@
       </c>
       <c r="G11" s="24"/>
     </row>
-    <row r="12" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
         <v>7</v>
       </c>
-      <c r="B12" s="58" t="s">
-        <v>400</v>
-      </c>
-      <c r="C12" s="57" t="s">
+      <c r="B12" s="57"/>
+      <c r="C12" s="59" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="48" t="s">
@@ -2437,12 +2129,12 @@
       </c>
       <c r="G12" s="21"/>
     </row>
-    <row r="13" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9">
         <v>8</v>
       </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="57"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="59"/>
       <c r="D13" s="50" t="s">
         <v>44</v>
       </c>
@@ -2454,14 +2146,12 @@
       </c>
       <c r="G13" s="24"/>
     </row>
-    <row r="14" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="42.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9">
         <v>9</v>
       </c>
-      <c r="B14" s="58" t="s">
-        <v>401</v>
-      </c>
-      <c r="C14" s="57" t="s">
+      <c r="B14" s="57"/>
+      <c r="C14" s="59" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="48" t="s">
@@ -2475,12 +2165,12 @@
       </c>
       <c r="G14" s="21"/>
     </row>
-    <row r="15" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A15" s="9">
         <v>10</v>
       </c>
-      <c r="B15" s="59"/>
-      <c r="C15" s="57"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="59"/>
       <c r="D15" s="49" t="s">
         <v>48</v>
       </c>
@@ -2492,14 +2182,12 @@
       </c>
       <c r="G15" s="24"/>
     </row>
-    <row r="16" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A16" s="9">
         <v>11</v>
       </c>
-      <c r="B16" s="58" t="s">
-        <v>402</v>
-      </c>
-      <c r="C16" s="57" t="s">
+      <c r="B16" s="57"/>
+      <c r="C16" s="59" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="48" t="s">
@@ -2513,12 +2201,12 @@
       </c>
       <c r="G16" s="21"/>
     </row>
-    <row r="17" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
         <v>12</v>
       </c>
-      <c r="B17" s="59"/>
-      <c r="C17" s="57"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="59"/>
       <c r="D17" s="49" t="s">
         <v>52</v>
       </c>
@@ -2530,14 +2218,12 @@
       </c>
       <c r="G17" s="24"/>
     </row>
-    <row r="18" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
         <v>13</v>
       </c>
-      <c r="B18" s="58" t="s">
-        <v>403</v>
-      </c>
-      <c r="C18" s="57" t="s">
+      <c r="B18" s="57"/>
+      <c r="C18" s="59" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="48" t="s">
@@ -2551,12 +2237,12 @@
       </c>
       <c r="G18" s="21"/>
     </row>
-    <row r="19" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
         <v>14</v>
       </c>
-      <c r="B19" s="59"/>
-      <c r="C19" s="57"/>
+      <c r="B19" s="58"/>
+      <c r="C19" s="59"/>
       <c r="D19" s="49" t="s">
         <v>63</v>
       </c>
@@ -2568,14 +2254,12 @@
       </c>
       <c r="G19" s="24"/>
     </row>
-    <row r="20" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>15</v>
       </c>
-      <c r="B20" s="58" t="s">
-        <v>404</v>
-      </c>
-      <c r="C20" s="57" t="s">
+      <c r="B20" s="57"/>
+      <c r="C20" s="59" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="48" t="s">
@@ -2591,12 +2275,12 @@
         <v>389</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>16</v>
       </c>
-      <c r="B21" s="59"/>
-      <c r="C21" s="57"/>
+      <c r="B21" s="58"/>
+      <c r="C21" s="59"/>
       <c r="D21" s="49" t="s">
         <v>67</v>
       </c>
@@ -2608,14 +2292,12 @@
       </c>
       <c r="G21" s="24"/>
     </row>
-    <row r="22" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
         <v>17</v>
       </c>
-      <c r="B22" s="58" t="s">
-        <v>405</v>
-      </c>
-      <c r="C22" s="57" t="s">
+      <c r="B22" s="57"/>
+      <c r="C22" s="59" t="s">
         <v>24</v>
       </c>
       <c r="D22" s="48" t="s">
@@ -2629,12 +2311,12 @@
       </c>
       <c r="G22" s="21"/>
     </row>
-    <row r="23" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
         <v>18</v>
       </c>
-      <c r="B23" s="59"/>
-      <c r="C23" s="57"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="59"/>
       <c r="D23" s="49" t="s">
         <v>70</v>
       </c>
@@ -2646,14 +2328,12 @@
       </c>
       <c r="G23" s="24"/>
     </row>
-    <row r="24" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A24" s="9">
         <v>19</v>
       </c>
-      <c r="B24" s="58" t="s">
-        <v>406</v>
-      </c>
-      <c r="C24" s="57" t="s">
+      <c r="B24" s="57"/>
+      <c r="C24" s="59" t="s">
         <v>25</v>
       </c>
       <c r="D24" s="48" t="s">
@@ -2667,12 +2347,12 @@
       </c>
       <c r="G24" s="21"/>
     </row>
-    <row r="25" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A25" s="9">
         <v>20</v>
       </c>
-      <c r="B25" s="59"/>
-      <c r="C25" s="57"/>
+      <c r="B25" s="58"/>
+      <c r="C25" s="59"/>
       <c r="D25" s="49" t="s">
         <v>75</v>
       </c>
@@ -2684,14 +2364,12 @@
       </c>
       <c r="G25" s="24"/>
     </row>
-    <row r="26" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A26" s="9">
         <v>21</v>
       </c>
-      <c r="B26" s="58" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="57" t="s">
+      <c r="B26" s="57"/>
+      <c r="C26" s="59" t="s">
         <v>26</v>
       </c>
       <c r="D26" s="48" t="s">
@@ -2705,12 +2383,12 @@
       </c>
       <c r="G26" s="21"/>
     </row>
-    <row r="27" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A27" s="9">
         <v>22</v>
       </c>
-      <c r="B27" s="59"/>
-      <c r="C27" s="57"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="59"/>
       <c r="D27" s="49" t="s">
         <v>79</v>
       </c>
@@ -2722,14 +2400,12 @@
       </c>
       <c r="G27" s="24"/>
     </row>
-    <row r="28" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A28" s="9">
         <v>23</v>
       </c>
-      <c r="B28" s="58" t="s">
-        <v>408</v>
-      </c>
-      <c r="C28" s="57" t="s">
+      <c r="B28" s="57"/>
+      <c r="C28" s="59" t="s">
         <v>16</v>
       </c>
       <c r="D28" s="48" t="s">
@@ -2743,12 +2419,12 @@
       </c>
       <c r="G28" s="21"/>
     </row>
-    <row r="29" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A29" s="9">
         <v>24</v>
       </c>
-      <c r="B29" s="59"/>
-      <c r="C29" s="57"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="59"/>
       <c r="D29" s="49" t="s">
         <v>83</v>
       </c>
@@ -2760,14 +2436,12 @@
       </c>
       <c r="G29" s="24"/>
     </row>
-    <row r="30" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A30" s="9">
         <v>25</v>
       </c>
-      <c r="B30" s="58" t="s">
-        <v>409</v>
-      </c>
-      <c r="C30" s="57" t="s">
+      <c r="B30" s="57"/>
+      <c r="C30" s="59" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="48" t="s">
@@ -2783,12 +2457,12 @@
         <v>389</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>26</v>
       </c>
-      <c r="B31" s="59"/>
-      <c r="C31" s="57"/>
+      <c r="B31" s="58"/>
+      <c r="C31" s="59"/>
       <c r="D31" s="49" t="s">
         <v>87</v>
       </c>
@@ -2800,14 +2474,12 @@
       </c>
       <c r="G31" s="24"/>
     </row>
-    <row r="32" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A32" s="9">
         <v>27</v>
       </c>
-      <c r="B32" s="58" t="s">
-        <v>410</v>
-      </c>
-      <c r="C32" s="57" t="s">
+      <c r="B32" s="57"/>
+      <c r="C32" s="59" t="s">
         <v>13</v>
       </c>
       <c r="D32" s="48" t="s">
@@ -2821,12 +2493,12 @@
       </c>
       <c r="G32" s="21"/>
     </row>
-    <row r="33" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A33" s="9">
         <v>28</v>
       </c>
-      <c r="B33" s="59"/>
-      <c r="C33" s="57"/>
+      <c r="B33" s="58"/>
+      <c r="C33" s="59"/>
       <c r="D33" s="49" t="s">
         <v>91</v>
       </c>
@@ -2838,14 +2510,12 @@
       </c>
       <c r="G33" s="24"/>
     </row>
-    <row r="34" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A34" s="9">
         <v>29</v>
       </c>
-      <c r="B34" s="58" t="s">
-        <v>411</v>
-      </c>
-      <c r="C34" s="60" t="s">
+      <c r="B34" s="57"/>
+      <c r="C34" s="64" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="48" t="s">
@@ -2859,12 +2529,12 @@
       </c>
       <c r="G34" s="21"/>
     </row>
-    <row r="35" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A35" s="9">
         <v>30</v>
       </c>
-      <c r="B35" s="59"/>
-      <c r="C35" s="60"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="64"/>
       <c r="D35" s="49" t="s">
         <v>95</v>
       </c>
@@ -2876,14 +2546,12 @@
       </c>
       <c r="G35" s="24"/>
     </row>
-    <row r="36" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A36" s="9">
         <v>31</v>
       </c>
-      <c r="B36" s="58" t="s">
-        <v>412</v>
-      </c>
-      <c r="C36" s="57" t="s">
+      <c r="B36" s="57"/>
+      <c r="C36" s="59" t="s">
         <v>12</v>
       </c>
       <c r="D36" s="48" t="s">
@@ -2899,12 +2567,12 @@
         <v>389</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>32</v>
       </c>
-      <c r="B37" s="59"/>
-      <c r="C37" s="57"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="59"/>
       <c r="D37" s="49" t="s">
         <v>99</v>
       </c>
@@ -2916,14 +2584,12 @@
       </c>
       <c r="G37" s="24"/>
     </row>
-    <row r="38" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A38" s="9">
         <v>33</v>
       </c>
-      <c r="B38" s="58" t="s">
-        <v>413</v>
-      </c>
-      <c r="C38" s="57" t="s">
+      <c r="B38" s="57"/>
+      <c r="C38" s="59" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="48" t="s">
@@ -2937,12 +2603,12 @@
       </c>
       <c r="G38" s="21"/>
     </row>
-    <row r="39" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A39" s="9">
         <v>34</v>
       </c>
-      <c r="B39" s="59"/>
-      <c r="C39" s="57"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="59"/>
       <c r="D39" s="49" t="s">
         <v>103</v>
       </c>
@@ -2954,14 +2620,12 @@
       </c>
       <c r="G39" s="24"/>
     </row>
-    <row r="40" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A40" s="9">
         <v>35</v>
       </c>
-      <c r="B40" s="58" t="s">
-        <v>414</v>
-      </c>
-      <c r="C40" s="57" t="s">
+      <c r="B40" s="57"/>
+      <c r="C40" s="59" t="s">
         <v>11</v>
       </c>
       <c r="D40" s="48" t="s">
@@ -2975,12 +2639,12 @@
       </c>
       <c r="G40" s="21"/>
     </row>
-    <row r="41" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A41" s="9">
         <v>36</v>
       </c>
-      <c r="B41" s="59"/>
-      <c r="C41" s="57"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="59"/>
       <c r="D41" s="49" t="s">
         <v>107</v>
       </c>
@@ -2992,14 +2656,12 @@
       </c>
       <c r="G41" s="24"/>
     </row>
-    <row r="42" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A42" s="9">
         <v>37</v>
       </c>
-      <c r="B42" s="58" t="s">
-        <v>415</v>
-      </c>
-      <c r="C42" s="61" t="s">
+      <c r="B42" s="57"/>
+      <c r="C42" s="67" t="s">
         <v>110</v>
       </c>
       <c r="D42" s="51" t="s">
@@ -3013,12 +2675,12 @@
       </c>
       <c r="G42" s="21"/>
     </row>
-    <row r="43" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A43" s="9">
         <v>38</v>
       </c>
-      <c r="B43" s="59"/>
-      <c r="C43" s="61"/>
+      <c r="B43" s="58"/>
+      <c r="C43" s="67"/>
       <c r="D43" s="50" t="s">
         <v>126</v>
       </c>
@@ -3030,14 +2692,12 @@
       </c>
       <c r="G43" s="24"/>
     </row>
-    <row r="44" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A44" s="9">
         <v>39</v>
       </c>
-      <c r="B44" s="58" t="s">
-        <v>416</v>
-      </c>
-      <c r="C44" s="57" t="s">
+      <c r="B44" s="57"/>
+      <c r="C44" s="59" t="s">
         <v>111</v>
       </c>
       <c r="D44" s="51" t="s">
@@ -3051,12 +2711,12 @@
       </c>
       <c r="G44" s="21"/>
     </row>
-    <row r="45" spans="1:7" ht="54" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A45" s="9">
         <v>40</v>
       </c>
-      <c r="B45" s="59"/>
-      <c r="C45" s="57"/>
+      <c r="B45" s="58"/>
+      <c r="C45" s="59"/>
       <c r="D45" s="50" t="s">
         <v>132</v>
       </c>
@@ -3068,14 +2728,12 @@
       </c>
       <c r="G45" s="24"/>
     </row>
-    <row r="46" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A46" s="9">
         <v>41</v>
       </c>
-      <c r="B46" s="58" t="s">
-        <v>417</v>
-      </c>
-      <c r="C46" s="57" t="s">
+      <c r="B46" s="57"/>
+      <c r="C46" s="59" t="s">
         <v>112</v>
       </c>
       <c r="D46" s="51" t="s">
@@ -3089,12 +2747,12 @@
       </c>
       <c r="G46" s="21"/>
     </row>
-    <row r="47" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A47" s="9">
         <v>42</v>
       </c>
-      <c r="B47" s="59"/>
-      <c r="C47" s="57"/>
+      <c r="B47" s="58"/>
+      <c r="C47" s="59"/>
       <c r="D47" s="50" t="s">
         <v>137</v>
       </c>
@@ -3106,14 +2764,12 @@
       </c>
       <c r="G47" s="24"/>
     </row>
-    <row r="48" spans="1:7" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="9">
         <v>43</v>
       </c>
-      <c r="B48" s="58" t="s">
-        <v>418</v>
-      </c>
-      <c r="C48" s="57" t="s">
+      <c r="B48" s="57"/>
+      <c r="C48" s="59" t="s">
         <v>113</v>
       </c>
       <c r="D48" s="51" t="s">
@@ -3127,12 +2783,12 @@
       </c>
       <c r="G48" s="21"/>
     </row>
-    <row r="49" spans="1:11" ht="36" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A49" s="9">
         <v>44</v>
       </c>
-      <c r="B49" s="59"/>
-      <c r="C49" s="57"/>
+      <c r="B49" s="58"/>
+      <c r="C49" s="59"/>
       <c r="D49" s="50" t="s">
         <v>141</v>
       </c>
@@ -3144,14 +2800,12 @@
       </c>
       <c r="G49" s="24"/>
     </row>
-    <row r="50" spans="1:11" ht="54" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A50" s="9">
         <v>45</v>
       </c>
-      <c r="B50" s="58" t="s">
-        <v>419</v>
-      </c>
-      <c r="C50" s="60" t="s">
+      <c r="B50" s="57"/>
+      <c r="C50" s="64" t="s">
         <v>4</v>
       </c>
       <c r="D50" s="51" t="s">
@@ -3165,12 +2819,12 @@
       </c>
       <c r="G50" s="21"/>
     </row>
-    <row r="51" spans="1:11" ht="54" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A51" s="9">
         <v>46</v>
       </c>
-      <c r="B51" s="59"/>
-      <c r="C51" s="60"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="64"/>
       <c r="D51" s="50" t="s">
         <v>146</v>
       </c>
@@ -3182,14 +2836,12 @@
       </c>
       <c r="G51" s="24"/>
     </row>
-    <row r="52" spans="1:11" ht="18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A52" s="9">
         <v>47</v>
       </c>
-      <c r="B52" s="58" t="s">
-        <v>420</v>
-      </c>
-      <c r="C52" s="57" t="s">
+      <c r="B52" s="57"/>
+      <c r="C52" s="59" t="s">
         <v>114</v>
       </c>
       <c r="D52" s="51" t="s">
@@ -3203,12 +2855,12 @@
       </c>
       <c r="G52" s="21"/>
     </row>
-    <row r="53" spans="1:11" ht="54" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A53" s="9">
         <v>48</v>
       </c>
-      <c r="B53" s="59"/>
-      <c r="C53" s="57"/>
+      <c r="B53" s="58"/>
+      <c r="C53" s="59"/>
       <c r="D53" s="50" t="s">
         <v>151</v>
       </c>
@@ -3220,14 +2872,12 @@
       </c>
       <c r="G53" s="24"/>
     </row>
-    <row r="54" spans="1:11" ht="18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A54" s="9">
         <v>49</v>
       </c>
-      <c r="B54" s="58" t="s">
-        <v>421</v>
-      </c>
-      <c r="C54" s="57" t="s">
+      <c r="B54" s="57"/>
+      <c r="C54" s="59" t="s">
         <v>115</v>
       </c>
       <c r="D54" s="51" t="s">
@@ -3241,12 +2891,12 @@
       </c>
       <c r="G54" s="21"/>
     </row>
-    <row r="55" spans="1:11" ht="36" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A55" s="9">
         <v>50</v>
       </c>
-      <c r="B55" s="59"/>
-      <c r="C55" s="57"/>
+      <c r="B55" s="58"/>
+      <c r="C55" s="59"/>
       <c r="D55" s="50" t="s">
         <v>156</v>
       </c>
@@ -3258,14 +2908,12 @@
       </c>
       <c r="G55" s="24"/>
     </row>
-    <row r="56" spans="1:11" ht="18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A56" s="9">
         <v>51</v>
       </c>
-      <c r="B56" s="58" t="s">
-        <v>422</v>
-      </c>
-      <c r="C56" s="57" t="s">
+      <c r="B56" s="57"/>
+      <c r="C56" s="59" t="s">
         <v>116</v>
       </c>
       <c r="D56" s="51" t="s">
@@ -3279,12 +2927,12 @@
       </c>
       <c r="G56" s="21"/>
     </row>
-    <row r="57" spans="1:11" ht="36" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A57" s="9">
         <v>52</v>
       </c>
-      <c r="B57" s="59"/>
-      <c r="C57" s="57"/>
+      <c r="B57" s="58"/>
+      <c r="C57" s="59"/>
       <c r="D57" s="50" t="s">
         <v>160</v>
       </c>
@@ -3296,14 +2944,12 @@
       </c>
       <c r="G57" s="24"/>
     </row>
-    <row r="58" spans="1:11" ht="18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A58" s="9">
         <v>53</v>
       </c>
-      <c r="B58" s="58" t="s">
-        <v>423</v>
-      </c>
-      <c r="C58" s="57" t="s">
+      <c r="B58" s="57"/>
+      <c r="C58" s="59" t="s">
         <v>117</v>
       </c>
       <c r="D58" s="51" t="s">
@@ -3317,12 +2963,12 @@
       </c>
       <c r="G58" s="21"/>
     </row>
-    <row r="59" spans="1:11" ht="36" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A59" s="9">
         <v>54</v>
       </c>
-      <c r="B59" s="59"/>
-      <c r="C59" s="57"/>
+      <c r="B59" s="58"/>
+      <c r="C59" s="59"/>
       <c r="D59" s="50" t="s">
         <v>165</v>
       </c>
@@ -3334,14 +2980,12 @@
       </c>
       <c r="G59" s="24"/>
     </row>
-    <row r="60" spans="1:11" ht="36" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A60" s="9">
         <v>55</v>
       </c>
-      <c r="B60" s="58" t="s">
-        <v>424</v>
-      </c>
-      <c r="C60" s="57" t="s">
+      <c r="B60" s="57"/>
+      <c r="C60" s="59" t="s">
         <v>118</v>
       </c>
       <c r="D60" s="51" t="s">
@@ -3358,12 +3002,12 @@
       <c r="J60" s="1"/>
       <c r="K60" s="5"/>
     </row>
-    <row r="61" spans="1:11" ht="36" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A61" s="9">
         <v>56</v>
       </c>
-      <c r="B61" s="59"/>
-      <c r="C61" s="57"/>
+      <c r="B61" s="58"/>
+      <c r="C61" s="59"/>
       <c r="D61" s="50" t="s">
         <v>170</v>
       </c>
@@ -3378,14 +3022,12 @@
       <c r="J61" s="1"/>
       <c r="K61" s="5"/>
     </row>
-    <row r="62" spans="1:11" ht="54" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A62" s="9">
         <v>57</v>
       </c>
-      <c r="B62" s="58" t="s">
-        <v>425</v>
-      </c>
-      <c r="C62" s="57" t="s">
+      <c r="B62" s="57"/>
+      <c r="C62" s="59" t="s">
         <v>119</v>
       </c>
       <c r="D62" s="51" t="s">
@@ -3402,12 +3044,12 @@
       <c r="J62" s="1"/>
       <c r="K62" s="2"/>
     </row>
-    <row r="63" spans="1:11" ht="54" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A63" s="9">
         <v>58</v>
       </c>
-      <c r="B63" s="59"/>
-      <c r="C63" s="57"/>
+      <c r="B63" s="58"/>
+      <c r="C63" s="59"/>
       <c r="D63" s="50" t="s">
         <v>174</v>
       </c>
@@ -3422,14 +3064,12 @@
       <c r="J63" s="1"/>
       <c r="K63" s="2"/>
     </row>
-    <row r="64" spans="1:11" ht="18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A64" s="9">
         <v>59</v>
       </c>
-      <c r="B64" s="62" t="s">
-        <v>426</v>
-      </c>
-      <c r="C64" s="60" t="s">
+      <c r="B64" s="65"/>
+      <c r="C64" s="64" t="s">
         <v>120</v>
       </c>
       <c r="D64" s="51" t="s">
@@ -3443,12 +3083,12 @@
       </c>
       <c r="G64" s="21"/>
     </row>
-    <row r="65" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A65" s="9">
         <v>60</v>
       </c>
-      <c r="B65" s="63"/>
-      <c r="C65" s="60"/>
+      <c r="B65" s="66"/>
+      <c r="C65" s="64"/>
       <c r="D65" s="50" t="s">
         <v>179</v>
       </c>
@@ -3460,14 +3100,12 @@
       </c>
       <c r="G65" s="24"/>
     </row>
-    <row r="66" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A66" s="9">
         <v>61</v>
       </c>
-      <c r="B66" s="58" t="s">
-        <v>427</v>
-      </c>
-      <c r="C66" s="57" t="s">
+      <c r="B66" s="57"/>
+      <c r="C66" s="59" t="s">
         <v>121</v>
       </c>
       <c r="D66" s="51" t="s">
@@ -3481,12 +3119,12 @@
       </c>
       <c r="G66" s="21"/>
     </row>
-    <row r="67" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A67" s="9">
         <v>62</v>
       </c>
-      <c r="B67" s="59"/>
-      <c r="C67" s="57"/>
+      <c r="B67" s="58"/>
+      <c r="C67" s="59"/>
       <c r="D67" s="50" t="s">
         <v>183</v>
       </c>
@@ -3498,14 +3136,12 @@
       </c>
       <c r="G67" s="24"/>
     </row>
-    <row r="68" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A68" s="9">
         <v>63</v>
       </c>
-      <c r="B68" s="58" t="s">
-        <v>428</v>
-      </c>
-      <c r="C68" s="57" t="s">
+      <c r="B68" s="57"/>
+      <c r="C68" s="59" t="s">
         <v>122</v>
       </c>
       <c r="D68" s="51" t="s">
@@ -3519,12 +3155,12 @@
       </c>
       <c r="G68" s="21"/>
     </row>
-    <row r="69" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A69" s="9">
         <v>64</v>
       </c>
-      <c r="B69" s="59"/>
-      <c r="C69" s="57"/>
+      <c r="B69" s="58"/>
+      <c r="C69" s="59"/>
       <c r="D69" s="50" t="s">
         <v>188</v>
       </c>
@@ -3536,14 +3172,12 @@
       </c>
       <c r="G69" s="24"/>
     </row>
-    <row r="70" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A70" s="9">
         <v>65</v>
       </c>
-      <c r="B70" s="58" t="s">
-        <v>429</v>
-      </c>
-      <c r="C70" s="57" t="s">
+      <c r="B70" s="57"/>
+      <c r="C70" s="59" t="s">
         <v>5</v>
       </c>
       <c r="D70" s="51" t="s">
@@ -3557,12 +3191,12 @@
       </c>
       <c r="G70" s="21"/>
     </row>
-    <row r="71" spans="1:9" ht="54" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" ht="56.25" x14ac:dyDescent="0.25">
       <c r="A71" s="9">
         <v>66</v>
       </c>
-      <c r="B71" s="59"/>
-      <c r="C71" s="57"/>
+      <c r="B71" s="58"/>
+      <c r="C71" s="59"/>
       <c r="D71" s="50" t="s">
         <v>192</v>
       </c>
@@ -3574,14 +3208,12 @@
       </c>
       <c r="G71" s="24"/>
     </row>
-    <row r="72" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A72" s="9">
         <v>67</v>
       </c>
-      <c r="B72" s="58" t="s">
-        <v>430</v>
-      </c>
-      <c r="C72" s="57" t="s">
+      <c r="B72" s="57"/>
+      <c r="C72" s="59" t="s">
         <v>195</v>
       </c>
       <c r="D72" s="48" t="s">
@@ -3595,12 +3227,12 @@
       </c>
       <c r="G72" s="21"/>
     </row>
-    <row r="73" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A73" s="9">
         <v>68</v>
       </c>
-      <c r="B73" s="59"/>
-      <c r="C73" s="57"/>
+      <c r="B73" s="58"/>
+      <c r="C73" s="59"/>
       <c r="D73" s="52" t="s">
         <v>253</v>
       </c>
@@ -3612,14 +3244,12 @@
       </c>
       <c r="G73" s="24"/>
     </row>
-    <row r="74" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>69</v>
       </c>
-      <c r="B74" s="58" t="s">
-        <v>431</v>
-      </c>
-      <c r="C74" s="57" t="s">
+      <c r="B74" s="57"/>
+      <c r="C74" s="59" t="s">
         <v>196</v>
       </c>
       <c r="D74" s="48" t="s">
@@ -3634,12 +3264,12 @@
       <c r="G74" s="38"/>
       <c r="I74" s="3"/>
     </row>
-    <row r="75" spans="1:9" ht="18" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A75" s="9">
         <v>70</v>
       </c>
-      <c r="B75" s="59"/>
-      <c r="C75" s="57"/>
+      <c r="B75" s="58"/>
+      <c r="C75" s="59"/>
       <c r="D75" s="52" t="s">
         <v>255</v>
       </c>
@@ -3652,13 +3282,11 @@
       <c r="G75" s="39"/>
       <c r="I75" s="4"/>
     </row>
-    <row r="76" spans="1:9" ht="36" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A76" s="9">
         <v>71</v>
       </c>
-      <c r="B76" s="14" t="s">
-        <v>432</v>
-      </c>
+      <c r="B76" s="14"/>
       <c r="C76" s="56" t="s">
         <v>197</v>
       </c>
@@ -3673,14 +3301,12 @@
       </c>
       <c r="G76" s="10"/>
     </row>
-    <row r="77" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A77" s="9">
         <v>72</v>
       </c>
-      <c r="B77" s="58" t="s">
-        <v>433</v>
-      </c>
-      <c r="C77" s="57" t="s">
+      <c r="B77" s="57"/>
+      <c r="C77" s="59" t="s">
         <v>198</v>
       </c>
       <c r="D77" s="48" t="s">
@@ -3694,12 +3320,12 @@
       </c>
       <c r="G77" s="21"/>
     </row>
-    <row r="78" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A78" s="9">
         <v>73</v>
       </c>
-      <c r="B78" s="59"/>
-      <c r="C78" s="57"/>
+      <c r="B78" s="58"/>
+      <c r="C78" s="59"/>
       <c r="D78" s="52" t="s">
         <v>257</v>
       </c>
@@ -3711,14 +3337,12 @@
       </c>
       <c r="G78" s="24"/>
     </row>
-    <row r="79" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A79" s="9">
         <v>74</v>
       </c>
-      <c r="B79" s="58" t="s">
-        <v>434</v>
-      </c>
-      <c r="C79" s="57" t="s">
+      <c r="B79" s="57"/>
+      <c r="C79" s="59" t="s">
         <v>199</v>
       </c>
       <c r="D79" s="48" t="s">
@@ -3732,12 +3356,12 @@
       </c>
       <c r="G79" s="21"/>
     </row>
-    <row r="80" spans="1:9" ht="18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A80" s="9">
         <v>75</v>
       </c>
-      <c r="B80" s="59"/>
-      <c r="C80" s="57"/>
+      <c r="B80" s="58"/>
+      <c r="C80" s="59"/>
       <c r="D80" s="52" t="s">
         <v>259</v>
       </c>
@@ -3749,14 +3373,12 @@
       </c>
       <c r="G80" s="24"/>
     </row>
-    <row r="81" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A81" s="9">
         <v>76</v>
       </c>
-      <c r="B81" s="58" t="s">
-        <v>435</v>
-      </c>
-      <c r="C81" s="57" t="s">
+      <c r="B81" s="57"/>
+      <c r="C81" s="59" t="s">
         <v>200</v>
       </c>
       <c r="D81" s="48" t="s">
@@ -3770,12 +3392,12 @@
       </c>
       <c r="G81" s="21"/>
     </row>
-    <row r="82" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A82" s="9">
         <v>77</v>
       </c>
-      <c r="B82" s="59"/>
-      <c r="C82" s="57"/>
+      <c r="B82" s="58"/>
+      <c r="C82" s="59"/>
       <c r="D82" s="52" t="s">
         <v>261</v>
       </c>
@@ -3787,14 +3409,12 @@
       </c>
       <c r="G82" s="24"/>
     </row>
-    <row r="83" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A83" s="9">
         <v>78</v>
       </c>
-      <c r="B83" s="58" t="s">
-        <v>436</v>
-      </c>
-      <c r="C83" s="57" t="s">
+      <c r="B83" s="57"/>
+      <c r="C83" s="59" t="s">
         <v>201</v>
       </c>
       <c r="D83" s="48" t="s">
@@ -3808,12 +3428,12 @@
       </c>
       <c r="G83" s="21"/>
     </row>
-    <row r="84" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A84" s="9">
         <v>79</v>
       </c>
-      <c r="B84" s="59"/>
-      <c r="C84" s="57"/>
+      <c r="B84" s="58"/>
+      <c r="C84" s="59"/>
       <c r="D84" s="52" t="s">
         <v>263</v>
       </c>
@@ -3825,14 +3445,12 @@
       </c>
       <c r="G84" s="24"/>
     </row>
-    <row r="85" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A85" s="9">
         <v>80</v>
       </c>
-      <c r="B85" s="58" t="s">
-        <v>437</v>
-      </c>
-      <c r="C85" s="57" t="s">
+      <c r="B85" s="57"/>
+      <c r="C85" s="59" t="s">
         <v>202</v>
       </c>
       <c r="D85" s="48" t="s">
@@ -3846,12 +3464,12 @@
       </c>
       <c r="G85" s="21"/>
     </row>
-    <row r="86" spans="1:7" ht="36" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>81</v>
       </c>
-      <c r="B86" s="59"/>
-      <c r="C86" s="57"/>
+      <c r="B86" s="58"/>
+      <c r="C86" s="59"/>
       <c r="D86" s="52" t="s">
         <v>265</v>
       </c>
@@ -3863,14 +3481,12 @@
       </c>
       <c r="G86" s="42"/>
     </row>
-    <row r="87" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A87" s="9">
         <v>82</v>
       </c>
-      <c r="B87" s="58" t="s">
-        <v>438</v>
-      </c>
-      <c r="C87" s="57" t="s">
+      <c r="B87" s="57"/>
+      <c r="C87" s="59" t="s">
         <v>203</v>
       </c>
       <c r="D87" s="48" t="s">
@@ -3884,12 +3500,12 @@
       </c>
       <c r="G87" s="21"/>
     </row>
-    <row r="88" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A88" s="9">
         <v>83</v>
       </c>
-      <c r="B88" s="59"/>
-      <c r="C88" s="57"/>
+      <c r="B88" s="58"/>
+      <c r="C88" s="59"/>
       <c r="D88" s="52" t="s">
         <v>267</v>
       </c>
@@ -3901,14 +3517,12 @@
       </c>
       <c r="G88" s="24"/>
     </row>
-    <row r="89" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A89" s="9">
         <v>84</v>
       </c>
-      <c r="B89" s="58" t="s">
-        <v>439</v>
-      </c>
-      <c r="C89" s="57" t="s">
+      <c r="B89" s="57"/>
+      <c r="C89" s="59" t="s">
         <v>6</v>
       </c>
       <c r="D89" s="48" t="s">
@@ -3922,12 +3536,12 @@
       </c>
       <c r="G89" s="21"/>
     </row>
-    <row r="90" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A90" s="9">
         <v>85</v>
       </c>
-      <c r="B90" s="59"/>
-      <c r="C90" s="57"/>
+      <c r="B90" s="58"/>
+      <c r="C90" s="59"/>
       <c r="D90" s="52" t="s">
         <v>269</v>
       </c>
@@ -3939,13 +3553,11 @@
       </c>
       <c r="G90" s="24"/>
     </row>
-    <row r="91" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A91" s="9">
         <v>86</v>
       </c>
-      <c r="B91" s="14" t="s">
-        <v>440</v>
-      </c>
+      <c r="B91" s="14"/>
       <c r="C91" s="56" t="s">
         <v>204</v>
       </c>
@@ -3960,14 +3572,12 @@
       </c>
       <c r="G91" s="10"/>
     </row>
-    <row r="92" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>87</v>
       </c>
-      <c r="B92" s="58" t="s">
-        <v>441</v>
-      </c>
-      <c r="C92" s="57" t="s">
+      <c r="B92" s="57"/>
+      <c r="C92" s="59" t="s">
         <v>205</v>
       </c>
       <c r="D92" s="48" t="s">
@@ -3983,12 +3593,12 @@
         <v>288</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="9">
         <v>88</v>
       </c>
-      <c r="B93" s="59"/>
-      <c r="C93" s="57"/>
+      <c r="B93" s="58"/>
+      <c r="C93" s="59"/>
       <c r="D93" s="52" t="s">
         <v>271</v>
       </c>
@@ -4000,14 +3610,12 @@
       </c>
       <c r="G93" s="42"/>
     </row>
-    <row r="94" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A94" s="9">
         <v>89</v>
       </c>
-      <c r="B94" s="58" t="s">
-        <v>442</v>
-      </c>
-      <c r="C94" s="57" t="s">
+      <c r="B94" s="57"/>
+      <c r="C94" s="59" t="s">
         <v>206</v>
       </c>
       <c r="D94" s="48" t="s">
@@ -4021,12 +3629,12 @@
       </c>
       <c r="G94" s="21"/>
     </row>
-    <row r="95" spans="1:7" ht="54" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" ht="75" x14ac:dyDescent="0.3">
       <c r="A95" s="9">
         <v>90</v>
       </c>
-      <c r="B95" s="59"/>
-      <c r="C95" s="57"/>
+      <c r="B95" s="58"/>
+      <c r="C95" s="59"/>
       <c r="D95" s="52" t="s">
         <v>273</v>
       </c>
@@ -4038,14 +3646,12 @@
       </c>
       <c r="G95" s="42"/>
     </row>
-    <row r="96" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>91</v>
       </c>
-      <c r="B96" s="58" t="s">
-        <v>443</v>
-      </c>
-      <c r="C96" s="57" t="s">
+      <c r="B96" s="57"/>
+      <c r="C96" s="59" t="s">
         <v>207</v>
       </c>
       <c r="D96" s="48" t="s">
@@ -4061,12 +3667,12 @@
         <v>288</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="9">
         <v>92</v>
       </c>
-      <c r="B97" s="59"/>
-      <c r="C97" s="57"/>
+      <c r="B97" s="58"/>
+      <c r="C97" s="59"/>
       <c r="D97" s="52" t="s">
         <v>275</v>
       </c>
@@ -4078,14 +3684,12 @@
       </c>
       <c r="G97" s="42"/>
     </row>
-    <row r="98" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="9">
         <v>93</v>
       </c>
-      <c r="B98" s="58" t="s">
-        <v>444</v>
-      </c>
-      <c r="C98" s="57" t="s">
+      <c r="B98" s="57"/>
+      <c r="C98" s="59" t="s">
         <v>208</v>
       </c>
       <c r="D98" s="48" t="s">
@@ -4101,12 +3705,12 @@
         <v>288</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>94</v>
       </c>
-      <c r="B99" s="59"/>
-      <c r="C99" s="57"/>
+      <c r="B99" s="58"/>
+      <c r="C99" s="59"/>
       <c r="D99" s="52" t="s">
         <v>277</v>
       </c>
@@ -4118,14 +3722,12 @@
       </c>
       <c r="G99" s="42"/>
     </row>
-    <row r="100" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A100" s="9">
         <v>95</v>
       </c>
-      <c r="B100" s="62" t="s">
-        <v>445</v>
-      </c>
-      <c r="C100" s="60" t="s">
+      <c r="B100" s="65"/>
+      <c r="C100" s="64" t="s">
         <v>209</v>
       </c>
       <c r="D100" s="48" t="s">
@@ -4139,12 +3741,12 @@
       </c>
       <c r="G100" s="21"/>
     </row>
-    <row r="101" spans="1:7" ht="36" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
         <v>96</v>
       </c>
-      <c r="B101" s="63"/>
-      <c r="C101" s="60"/>
+      <c r="B101" s="66"/>
+      <c r="C101" s="64"/>
       <c r="D101" s="52" t="s">
         <v>279</v>
       </c>
@@ -4156,13 +3758,11 @@
       </c>
       <c r="G101" s="42"/>
     </row>
-    <row r="102" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>97</v>
       </c>
-      <c r="B102" s="14" t="s">
-        <v>446</v>
-      </c>
+      <c r="B102" s="14"/>
       <c r="C102" s="56" t="s">
         <v>210</v>
       </c>
@@ -4177,14 +3777,12 @@
       </c>
       <c r="G102" s="12"/>
     </row>
-    <row r="103" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A103" s="9">
         <v>98</v>
       </c>
-      <c r="B103" s="58" t="s">
-        <v>447</v>
-      </c>
-      <c r="C103" s="57" t="s">
+      <c r="B103" s="57"/>
+      <c r="C103" s="59" t="s">
         <v>211</v>
       </c>
       <c r="D103" s="48" t="s">
@@ -4198,12 +3796,12 @@
       </c>
       <c r="G103" s="21"/>
     </row>
-    <row r="104" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A104" s="9">
         <v>99</v>
       </c>
-      <c r="B104" s="59"/>
-      <c r="C104" s="57"/>
+      <c r="B104" s="58"/>
+      <c r="C104" s="59"/>
       <c r="D104" s="52" t="s">
         <v>281</v>
       </c>
@@ -4215,14 +3813,12 @@
       </c>
       <c r="G104" s="24"/>
     </row>
-    <row r="105" spans="1:7" ht="54" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" ht="56.25" x14ac:dyDescent="0.3">
       <c r="A105" s="9">
         <v>100</v>
       </c>
-      <c r="B105" s="58" t="s">
-        <v>448</v>
-      </c>
-      <c r="C105" s="57" t="s">
+      <c r="B105" s="57"/>
+      <c r="C105" s="59" t="s">
         <v>212</v>
       </c>
       <c r="D105" s="48" t="s">
@@ -4236,12 +3832,12 @@
       </c>
       <c r="G105" s="44"/>
     </row>
-    <row r="106" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A106" s="9">
         <v>101</v>
       </c>
-      <c r="B106" s="59"/>
-      <c r="C106" s="57"/>
+      <c r="B106" s="58"/>
+      <c r="C106" s="59"/>
       <c r="D106" s="52" t="s">
         <v>283</v>
       </c>
@@ -4253,14 +3849,12 @@
       </c>
       <c r="G106" s="24"/>
     </row>
-    <row r="107" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A107" s="9">
         <v>102</v>
       </c>
-      <c r="B107" s="58" t="s">
-        <v>449</v>
-      </c>
-      <c r="C107" s="57" t="s">
+      <c r="B107" s="57"/>
+      <c r="C107" s="59" t="s">
         <v>7</v>
       </c>
       <c r="D107" s="51" t="s">
@@ -4274,12 +3868,12 @@
       </c>
       <c r="G107" s="21"/>
     </row>
-    <row r="108" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A108" s="9">
         <v>103</v>
       </c>
-      <c r="B108" s="59"/>
-      <c r="C108" s="57"/>
+      <c r="B108" s="58"/>
+      <c r="C108" s="59"/>
       <c r="D108" s="50" t="s">
         <v>310</v>
       </c>
@@ -4291,14 +3885,12 @@
       </c>
       <c r="G108" s="24"/>
     </row>
-    <row r="109" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A109" s="9">
         <v>104</v>
       </c>
-      <c r="B109" s="58" t="s">
-        <v>450</v>
-      </c>
-      <c r="C109" s="57" t="s">
+      <c r="B109" s="57"/>
+      <c r="C109" s="59" t="s">
         <v>289</v>
       </c>
       <c r="D109" s="51" t="s">
@@ -4312,12 +3904,12 @@
       </c>
       <c r="G109" s="21"/>
     </row>
-    <row r="110" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A110" s="9">
         <v>105</v>
       </c>
-      <c r="B110" s="59"/>
-      <c r="C110" s="57"/>
+      <c r="B110" s="58"/>
+      <c r="C110" s="59"/>
       <c r="D110" s="50" t="s">
         <v>313</v>
       </c>
@@ -4329,13 +3921,11 @@
       </c>
       <c r="G110" s="24"/>
     </row>
-    <row r="111" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A111" s="9">
         <v>106</v>
       </c>
-      <c r="B111" s="14" t="s">
-        <v>451</v>
-      </c>
+      <c r="B111" s="14"/>
       <c r="C111" s="56" t="s">
         <v>290</v>
       </c>
@@ -4350,14 +3940,12 @@
       </c>
       <c r="G111" s="10"/>
     </row>
-    <row r="112" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A112" s="9">
         <v>107</v>
       </c>
-      <c r="B112" s="58" t="s">
-        <v>452</v>
-      </c>
-      <c r="C112" s="57" t="s">
+      <c r="B112" s="57"/>
+      <c r="C112" s="59" t="s">
         <v>291</v>
       </c>
       <c r="D112" s="51" t="s">
@@ -4371,12 +3959,12 @@
       </c>
       <c r="G112" s="21"/>
     </row>
-    <row r="113" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A113" s="9">
         <v>108</v>
       </c>
-      <c r="B113" s="59"/>
-      <c r="C113" s="57"/>
+      <c r="B113" s="58"/>
+      <c r="C113" s="59"/>
       <c r="D113" s="50" t="s">
         <v>316</v>
       </c>
@@ -4388,14 +3976,12 @@
       </c>
       <c r="G113" s="24"/>
     </row>
-    <row r="114" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A114" s="9">
         <v>109</v>
       </c>
-      <c r="B114" s="58" t="s">
-        <v>453</v>
-      </c>
-      <c r="C114" s="57" t="s">
+      <c r="B114" s="57"/>
+      <c r="C114" s="59" t="s">
         <v>292</v>
       </c>
       <c r="D114" s="51" t="s">
@@ -4409,12 +3995,12 @@
       </c>
       <c r="G114" s="21"/>
     </row>
-    <row r="115" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A115" s="9">
         <v>110</v>
       </c>
-      <c r="B115" s="59"/>
-      <c r="C115" s="57"/>
+      <c r="B115" s="58"/>
+      <c r="C115" s="59"/>
       <c r="D115" s="50" t="s">
         <v>318</v>
       </c>
@@ -4426,13 +4012,11 @@
       </c>
       <c r="G115" s="24"/>
     </row>
-    <row r="116" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A116" s="9">
         <v>111</v>
       </c>
-      <c r="B116" s="14" t="s">
-        <v>454</v>
-      </c>
+      <c r="B116" s="14"/>
       <c r="C116" s="56" t="s">
         <v>293</v>
       </c>
@@ -4447,14 +4031,12 @@
       </c>
       <c r="G116" s="10"/>
     </row>
-    <row r="117" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A117" s="9">
         <v>112</v>
       </c>
-      <c r="B117" s="58" t="s">
-        <v>455</v>
-      </c>
-      <c r="C117" s="57" t="s">
+      <c r="B117" s="57"/>
+      <c r="C117" s="59" t="s">
         <v>294</v>
       </c>
       <c r="D117" s="51" t="s">
@@ -4468,12 +4050,12 @@
       </c>
       <c r="G117" s="21"/>
     </row>
-    <row r="118" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A118" s="9">
         <v>113</v>
       </c>
-      <c r="B118" s="59"/>
-      <c r="C118" s="57"/>
+      <c r="B118" s="58"/>
+      <c r="C118" s="59"/>
       <c r="D118" s="50" t="s">
         <v>321</v>
       </c>
@@ -4485,14 +4067,12 @@
       </c>
       <c r="G118" s="24"/>
     </row>
-    <row r="119" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A119" s="9">
         <v>114</v>
       </c>
-      <c r="B119" s="58" t="s">
-        <v>456</v>
-      </c>
-      <c r="C119" s="57" t="s">
+      <c r="B119" s="57"/>
+      <c r="C119" s="59" t="s">
         <v>295</v>
       </c>
       <c r="D119" s="51" t="s">
@@ -4506,12 +4086,12 @@
       </c>
       <c r="G119" s="21"/>
     </row>
-    <row r="120" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A120" s="9">
         <v>115</v>
       </c>
-      <c r="B120" s="59"/>
-      <c r="C120" s="57"/>
+      <c r="B120" s="58"/>
+      <c r="C120" s="59"/>
       <c r="D120" s="50" t="s">
         <v>323</v>
       </c>
@@ -4523,14 +4103,12 @@
       </c>
       <c r="G120" s="24"/>
     </row>
-    <row r="121" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A121" s="9">
         <v>116</v>
       </c>
-      <c r="B121" s="58" t="s">
-        <v>457</v>
-      </c>
-      <c r="C121" s="57" t="s">
+      <c r="B121" s="57"/>
+      <c r="C121" s="59" t="s">
         <v>296</v>
       </c>
       <c r="D121" s="51" t="s">
@@ -4544,12 +4122,12 @@
       </c>
       <c r="G121" s="21"/>
     </row>
-    <row r="122" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A122" s="9">
         <v>117</v>
       </c>
-      <c r="B122" s="59"/>
-      <c r="C122" s="57"/>
+      <c r="B122" s="58"/>
+      <c r="C122" s="59"/>
       <c r="D122" s="50" t="s">
         <v>325</v>
       </c>
@@ -4561,14 +4139,12 @@
       </c>
       <c r="G122" s="24"/>
     </row>
-    <row r="123" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A123" s="9">
         <v>118</v>
       </c>
-      <c r="B123" s="58" t="s">
-        <v>458</v>
-      </c>
-      <c r="C123" s="57" t="s">
+      <c r="B123" s="57"/>
+      <c r="C123" s="59" t="s">
         <v>297</v>
       </c>
       <c r="D123" s="51" t="s">
@@ -4582,12 +4158,12 @@
       </c>
       <c r="G123" s="21"/>
     </row>
-    <row r="124" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A124" s="9">
         <v>119</v>
       </c>
-      <c r="B124" s="59"/>
-      <c r="C124" s="57"/>
+      <c r="B124" s="58"/>
+      <c r="C124" s="59"/>
       <c r="D124" s="50" t="s">
         <v>327</v>
       </c>
@@ -4599,14 +4175,12 @@
       </c>
       <c r="G124" s="24"/>
     </row>
-    <row r="125" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A125" s="9">
         <v>120</v>
       </c>
-      <c r="B125" s="58" t="s">
-        <v>459</v>
-      </c>
-      <c r="C125" s="57" t="s">
+      <c r="B125" s="57"/>
+      <c r="C125" s="59" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="51" t="s">
@@ -4620,12 +4194,12 @@
       </c>
       <c r="G125" s="21"/>
     </row>
-    <row r="126" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A126" s="9">
         <v>121</v>
       </c>
-      <c r="B126" s="59"/>
-      <c r="C126" s="57"/>
+      <c r="B126" s="58"/>
+      <c r="C126" s="59"/>
       <c r="D126" s="50" t="s">
         <v>329</v>
       </c>
@@ -4637,13 +4211,11 @@
       </c>
       <c r="G126" s="24"/>
     </row>
-    <row r="127" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A127" s="9">
         <v>122</v>
       </c>
-      <c r="B127" s="14" t="s">
-        <v>460</v>
-      </c>
+      <c r="B127" s="14"/>
       <c r="C127" s="56" t="s">
         <v>298</v>
       </c>
@@ -4658,14 +4230,12 @@
       </c>
       <c r="G127" s="10"/>
     </row>
-    <row r="128" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A128" s="9">
         <v>123</v>
       </c>
-      <c r="B128" s="58" t="s">
-        <v>461</v>
-      </c>
-      <c r="C128" s="57" t="s">
+      <c r="B128" s="57"/>
+      <c r="C128" s="59" t="s">
         <v>299</v>
       </c>
       <c r="D128" s="51" t="s">
@@ -4675,16 +4245,16 @@
         <v>124</v>
       </c>
       <c r="F128" s="46" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="G128" s="21"/>
     </row>
-    <row r="129" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A129" s="9">
         <v>124</v>
       </c>
-      <c r="B129" s="59"/>
-      <c r="C129" s="57"/>
+      <c r="B129" s="58"/>
+      <c r="C129" s="59"/>
       <c r="D129" s="50" t="s">
         <v>332</v>
       </c>
@@ -4696,13 +4266,11 @@
       </c>
       <c r="G129" s="24"/>
     </row>
-    <row r="130" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A130" s="9">
         <v>125</v>
       </c>
-      <c r="B130" s="14" t="s">
-        <v>462</v>
-      </c>
+      <c r="B130" s="14"/>
       <c r="C130" s="56" t="s">
         <v>300</v>
       </c>
@@ -4717,13 +4285,11 @@
       </c>
       <c r="G130" s="10"/>
     </row>
-    <row r="131" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A131" s="9">
         <v>126</v>
       </c>
-      <c r="B131" s="14" t="s">
-        <v>463</v>
-      </c>
+      <c r="B131" s="14"/>
       <c r="C131" s="56" t="s">
         <v>301</v>
       </c>
@@ -4738,14 +4304,12 @@
       </c>
       <c r="G131" s="10"/>
     </row>
-    <row r="132" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A132" s="9">
         <v>127</v>
       </c>
-      <c r="B132" s="58" t="s">
-        <v>464</v>
-      </c>
-      <c r="C132" s="57" t="s">
+      <c r="B132" s="57"/>
+      <c r="C132" s="59" t="s">
         <v>302</v>
       </c>
       <c r="D132" s="51" t="s">
@@ -4759,12 +4323,12 @@
       </c>
       <c r="G132" s="21"/>
     </row>
-    <row r="133" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A133" s="9">
         <v>128</v>
       </c>
-      <c r="B133" s="59"/>
-      <c r="C133" s="57"/>
+      <c r="B133" s="58"/>
+      <c r="C133" s="59"/>
       <c r="D133" s="50" t="s">
         <v>336</v>
       </c>
@@ -4776,14 +4340,12 @@
       </c>
       <c r="G133" s="24"/>
     </row>
-    <row r="134" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A134" s="9">
         <v>129</v>
       </c>
-      <c r="B134" s="58" t="s">
-        <v>465</v>
-      </c>
-      <c r="C134" s="57" t="s">
+      <c r="B134" s="57"/>
+      <c r="C134" s="59" t="s">
         <v>303</v>
       </c>
       <c r="D134" s="51" t="s">
@@ -4797,12 +4359,12 @@
       </c>
       <c r="G134" s="21"/>
     </row>
-    <row r="135" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A135" s="9">
         <v>130</v>
       </c>
-      <c r="B135" s="59"/>
-      <c r="C135" s="57"/>
+      <c r="B135" s="58"/>
+      <c r="C135" s="59"/>
       <c r="D135" s="50" t="s">
         <v>338</v>
       </c>
@@ -4814,13 +4376,11 @@
       </c>
       <c r="G135" s="24"/>
     </row>
-    <row r="136" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A136" s="9">
         <v>131</v>
       </c>
-      <c r="B136" s="14" t="s">
-        <v>466</v>
-      </c>
+      <c r="B136" s="14"/>
       <c r="C136" s="56" t="s">
         <v>304</v>
       </c>
@@ -4835,14 +4395,12 @@
       </c>
       <c r="G136" s="10"/>
     </row>
-    <row r="137" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A137" s="9">
         <v>132</v>
       </c>
-      <c r="B137" s="58" t="s">
-        <v>467</v>
-      </c>
-      <c r="C137" s="57" t="s">
+      <c r="B137" s="57"/>
+      <c r="C137" s="59" t="s">
         <v>305</v>
       </c>
       <c r="D137" s="51" t="s">
@@ -4856,12 +4414,12 @@
       </c>
       <c r="G137" s="21"/>
     </row>
-    <row r="138" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A138" s="9">
         <v>133</v>
       </c>
-      <c r="B138" s="59"/>
-      <c r="C138" s="57"/>
+      <c r="B138" s="58"/>
+      <c r="C138" s="59"/>
       <c r="D138" s="50" t="s">
         <v>341</v>
       </c>
@@ -4873,14 +4431,12 @@
       </c>
       <c r="G138" s="24"/>
     </row>
-    <row r="139" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A139" s="9">
         <v>134</v>
       </c>
-      <c r="B139" s="58" t="s">
-        <v>468</v>
-      </c>
-      <c r="C139" s="60" t="s">
+      <c r="B139" s="57"/>
+      <c r="C139" s="64" t="s">
         <v>306</v>
       </c>
       <c r="D139" s="51" t="s">
@@ -4894,12 +4450,12 @@
       </c>
       <c r="G139" s="21"/>
     </row>
-    <row r="140" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A140" s="9">
         <v>135</v>
       </c>
-      <c r="B140" s="59"/>
-      <c r="C140" s="60"/>
+      <c r="B140" s="58"/>
+      <c r="C140" s="64"/>
       <c r="D140" s="50" t="s">
         <v>343</v>
       </c>
@@ -4911,13 +4467,11 @@
       </c>
       <c r="G140" s="24"/>
     </row>
-    <row r="141" spans="1:7" ht="36" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A141" s="9">
         <v>136</v>
       </c>
-      <c r="B141" s="14" t="s">
-        <v>469</v>
-      </c>
+      <c r="B141" s="14"/>
       <c r="C141" s="56" t="s">
         <v>9</v>
       </c>
@@ -4932,14 +4486,12 @@
       </c>
       <c r="G141" s="10"/>
     </row>
-    <row r="142" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A142" s="9">
         <v>137</v>
       </c>
-      <c r="B142" s="58" t="s">
-        <v>470</v>
-      </c>
-      <c r="C142" s="57" t="s">
+      <c r="B142" s="57"/>
+      <c r="C142" s="59" t="s">
         <v>307</v>
       </c>
       <c r="D142" s="51" t="s">
@@ -4953,12 +4505,12 @@
       </c>
       <c r="G142" s="21"/>
     </row>
-    <row r="143" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A143" s="9">
         <v>138</v>
       </c>
-      <c r="B143" s="59"/>
-      <c r="C143" s="57"/>
+      <c r="B143" s="58"/>
+      <c r="C143" s="59"/>
       <c r="D143" s="50" t="s">
         <v>346</v>
       </c>
@@ -4970,14 +4522,12 @@
       </c>
       <c r="G143" s="24"/>
     </row>
-    <row r="144" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A144" s="9">
         <v>139</v>
       </c>
-      <c r="B144" s="58" t="s">
-        <v>471</v>
-      </c>
-      <c r="C144" s="57" t="s">
+      <c r="B144" s="57"/>
+      <c r="C144" s="59" t="s">
         <v>308</v>
       </c>
       <c r="D144" s="51" t="s">
@@ -4991,12 +4541,12 @@
       </c>
       <c r="G144" s="21"/>
     </row>
-    <row r="145" spans="1:7" ht="18" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A145" s="9">
         <v>140</v>
       </c>
-      <c r="B145" s="59"/>
-      <c r="C145" s="57"/>
+      <c r="B145" s="58"/>
+      <c r="C145" s="59"/>
       <c r="D145" s="50" t="s">
         <v>349</v>
       </c>
@@ -5008,24 +4558,133 @@
       </c>
       <c r="G145" s="24"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B146" s="55"/>
       <c r="C146" s="55"/>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B147" s="55"/>
       <c r="C147" s="55"/>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B148" s="55"/>
       <c r="C148" s="55"/>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B149" s="55"/>
       <c r="C149" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="133">
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="C112:C113"/>
     <mergeCell ref="B144:B145"/>
     <mergeCell ref="C144:C145"/>
     <mergeCell ref="A1:C1"/>
@@ -5050,115 +4709,6 @@
     <mergeCell ref="B125:B126"/>
     <mergeCell ref="C125:C126"/>
     <mergeCell ref="B114:B115"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="C117:C118"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="B107:B108"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="C112:C113"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="C103:C104"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/knowledge/data/DANH SÁCH BÍ THƯ, TRƯỞNG KHU PHỐ PHƯỜNG TÂN HƯNG MỚI (1).xlsx
+++ b/knowledge/data/DANH SÁCH BÍ THƯ, TRƯỞNG KHU PHỐ PHƯỜNG TÂN HƯNG MỚI (1).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\vn_testing\backend\knowledge\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18679103-21AB-45AB-BAE6-47B09CC04645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8895B226-8BE6-4F03-93A8-8D45A9360EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1080" windowWidth="21600" windowHeight="11295" xr2:uid="{7661DE85-3A2C-4118-BFA6-14A974D2AA07}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="396">
   <si>
     <t>Họ và tên</t>
   </si>
@@ -367,10 +367,6 @@
   </si>
   <si>
     <t>0903718803</t>
-  </si>
-  <si>
-    <t>Tên Khu phố
-Phường cũ</t>
   </si>
   <si>
     <t>Khu phố 19</t>
@@ -1591,6 +1587,9 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1598,7 +1597,16 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1611,18 +1619,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1956,38 +1952,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="64" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="66" t="s">
+        <v>389</v>
+      </c>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+    </row>
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="67" t="s">
         <v>391</v>
       </c>
-      <c r="B1" s="61"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="62" t="s">
-        <v>390</v>
-      </c>
-      <c r="F1" s="61"/>
-      <c r="G1" s="61"/>
-    </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="63" t="s">
-        <v>392</v>
-      </c>
-      <c r="B3" s="63"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="63"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="67"/>
+      <c r="E3" s="67"/>
+      <c r="F3" s="67"/>
+      <c r="G3" s="67"/>
     </row>
     <row r="5" spans="1:7" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>109</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="B5" s="8"/>
       <c r="C5" s="8" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>0</v>
@@ -1996,7 +1990,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>2</v>
@@ -2006,8 +2000,8 @@
       <c r="A6" s="9">
         <v>1</v>
       </c>
-      <c r="B6" s="57"/>
-      <c r="C6" s="59" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="57" t="s">
         <v>15</v>
       </c>
       <c r="D6" s="48" t="s">
@@ -2025,8 +2019,8 @@
       <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="59"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="49" t="s">
         <v>29</v>
       </c>
@@ -2042,8 +2036,8 @@
       <c r="A8" s="9">
         <v>3</v>
       </c>
-      <c r="B8" s="57"/>
-      <c r="C8" s="59" t="s">
+      <c r="B8" s="58"/>
+      <c r="C8" s="57" t="s">
         <v>17</v>
       </c>
       <c r="D8" s="48" t="s">
@@ -2061,8 +2055,8 @@
       <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="59"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="57"/>
       <c r="D9" s="49" t="s">
         <v>35</v>
       </c>
@@ -2078,8 +2072,8 @@
       <c r="A10" s="9">
         <v>5</v>
       </c>
-      <c r="B10" s="57"/>
-      <c r="C10" s="59" t="s">
+      <c r="B10" s="58"/>
+      <c r="C10" s="57" t="s">
         <v>18</v>
       </c>
       <c r="D10" s="48" t="s">
@@ -2097,8 +2091,8 @@
       <c r="A11" s="9">
         <v>6</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="59"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="57"/>
       <c r="D11" s="49" t="s">
         <v>40</v>
       </c>
@@ -2114,8 +2108,8 @@
       <c r="A12" s="9">
         <v>7</v>
       </c>
-      <c r="B12" s="57"/>
-      <c r="C12" s="59" t="s">
+      <c r="B12" s="58"/>
+      <c r="C12" s="57" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="48" t="s">
@@ -2133,8 +2127,8 @@
       <c r="A13" s="9">
         <v>8</v>
       </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="59"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="57"/>
       <c r="D13" s="50" t="s">
         <v>44</v>
       </c>
@@ -2150,8 +2144,8 @@
       <c r="A14" s="9">
         <v>9</v>
       </c>
-      <c r="B14" s="57"/>
-      <c r="C14" s="59" t="s">
+      <c r="B14" s="58"/>
+      <c r="C14" s="57" t="s">
         <v>20</v>
       </c>
       <c r="D14" s="48" t="s">
@@ -2169,8 +2163,8 @@
       <c r="A15" s="9">
         <v>10</v>
       </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="59"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="57"/>
       <c r="D15" s="49" t="s">
         <v>48</v>
       </c>
@@ -2186,8 +2180,8 @@
       <c r="A16" s="9">
         <v>11</v>
       </c>
-      <c r="B16" s="57"/>
-      <c r="C16" s="59" t="s">
+      <c r="B16" s="58"/>
+      <c r="C16" s="57" t="s">
         <v>22</v>
       </c>
       <c r="D16" s="48" t="s">
@@ -2205,8 +2199,8 @@
       <c r="A17" s="9">
         <v>12</v>
       </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="59"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="57"/>
       <c r="D17" s="49" t="s">
         <v>52</v>
       </c>
@@ -2222,8 +2216,8 @@
       <c r="A18" s="9">
         <v>13</v>
       </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="59" t="s">
+      <c r="B18" s="58"/>
+      <c r="C18" s="57" t="s">
         <v>23</v>
       </c>
       <c r="D18" s="48" t="s">
@@ -2241,8 +2235,8 @@
       <c r="A19" s="9">
         <v>14</v>
       </c>
-      <c r="B19" s="58"/>
-      <c r="C19" s="59"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="57"/>
       <c r="D19" s="49" t="s">
         <v>63</v>
       </c>
@@ -2258,8 +2252,8 @@
       <c r="A20" s="9">
         <v>15</v>
       </c>
-      <c r="B20" s="57"/>
-      <c r="C20" s="59" t="s">
+      <c r="B20" s="58"/>
+      <c r="C20" s="57" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="48" t="s">
@@ -2272,15 +2266,15 @@
         <v>66</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
         <v>16</v>
       </c>
-      <c r="B21" s="58"/>
-      <c r="C21" s="59"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="57"/>
       <c r="D21" s="49" t="s">
         <v>67</v>
       </c>
@@ -2288,7 +2282,7 @@
         <v>37</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="G21" s="24"/>
     </row>
@@ -2296,8 +2290,8 @@
       <c r="A22" s="9">
         <v>17</v>
       </c>
-      <c r="B22" s="57"/>
-      <c r="C22" s="59" t="s">
+      <c r="B22" s="58"/>
+      <c r="C22" s="57" t="s">
         <v>24</v>
       </c>
       <c r="D22" s="48" t="s">
@@ -2315,8 +2309,8 @@
       <c r="A23" s="9">
         <v>18</v>
       </c>
-      <c r="B23" s="58"/>
-      <c r="C23" s="59"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="57"/>
       <c r="D23" s="49" t="s">
         <v>70</v>
       </c>
@@ -2332,8 +2326,8 @@
       <c r="A24" s="9">
         <v>19</v>
       </c>
-      <c r="B24" s="57"/>
-      <c r="C24" s="59" t="s">
+      <c r="B24" s="58"/>
+      <c r="C24" s="57" t="s">
         <v>25</v>
       </c>
       <c r="D24" s="48" t="s">
@@ -2351,8 +2345,8 @@
       <c r="A25" s="9">
         <v>20</v>
       </c>
-      <c r="B25" s="58"/>
-      <c r="C25" s="59"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="57"/>
       <c r="D25" s="49" t="s">
         <v>75</v>
       </c>
@@ -2368,8 +2362,8 @@
       <c r="A26" s="9">
         <v>21</v>
       </c>
-      <c r="B26" s="57"/>
-      <c r="C26" s="59" t="s">
+      <c r="B26" s="58"/>
+      <c r="C26" s="57" t="s">
         <v>26</v>
       </c>
       <c r="D26" s="48" t="s">
@@ -2387,8 +2381,8 @@
       <c r="A27" s="9">
         <v>22</v>
       </c>
-      <c r="B27" s="58"/>
-      <c r="C27" s="59"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="57"/>
       <c r="D27" s="49" t="s">
         <v>79</v>
       </c>
@@ -2404,8 +2398,8 @@
       <c r="A28" s="9">
         <v>23</v>
       </c>
-      <c r="B28" s="57"/>
-      <c r="C28" s="59" t="s">
+      <c r="B28" s="58"/>
+      <c r="C28" s="57" t="s">
         <v>16</v>
       </c>
       <c r="D28" s="48" t="s">
@@ -2423,8 +2417,8 @@
       <c r="A29" s="9">
         <v>24</v>
       </c>
-      <c r="B29" s="58"/>
-      <c r="C29" s="59"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="57"/>
       <c r="D29" s="49" t="s">
         <v>83</v>
       </c>
@@ -2440,8 +2434,8 @@
       <c r="A30" s="9">
         <v>25</v>
       </c>
-      <c r="B30" s="57"/>
-      <c r="C30" s="59" t="s">
+      <c r="B30" s="58"/>
+      <c r="C30" s="57" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="48" t="s">
@@ -2454,15 +2448,15 @@
         <v>86</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A31" s="9">
         <v>26</v>
       </c>
-      <c r="B31" s="58"/>
-      <c r="C31" s="59"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="57"/>
       <c r="D31" s="49" t="s">
         <v>87</v>
       </c>
@@ -2478,8 +2472,8 @@
       <c r="A32" s="9">
         <v>27</v>
       </c>
-      <c r="B32" s="57"/>
-      <c r="C32" s="59" t="s">
+      <c r="B32" s="58"/>
+      <c r="C32" s="57" t="s">
         <v>13</v>
       </c>
       <c r="D32" s="48" t="s">
@@ -2497,8 +2491,8 @@
       <c r="A33" s="9">
         <v>28</v>
       </c>
-      <c r="B33" s="58"/>
-      <c r="C33" s="59"/>
+      <c r="B33" s="59"/>
+      <c r="C33" s="57"/>
       <c r="D33" s="49" t="s">
         <v>91</v>
       </c>
@@ -2514,8 +2508,8 @@
       <c r="A34" s="9">
         <v>29</v>
       </c>
-      <c r="B34" s="57"/>
-      <c r="C34" s="64" t="s">
+      <c r="B34" s="58"/>
+      <c r="C34" s="60" t="s">
         <v>10</v>
       </c>
       <c r="D34" s="48" t="s">
@@ -2533,8 +2527,8 @@
       <c r="A35" s="9">
         <v>30</v>
       </c>
-      <c r="B35" s="58"/>
-      <c r="C35" s="64"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="60"/>
       <c r="D35" s="49" t="s">
         <v>95</v>
       </c>
@@ -2550,8 +2544,8 @@
       <c r="A36" s="9">
         <v>31</v>
       </c>
-      <c r="B36" s="57"/>
-      <c r="C36" s="59" t="s">
+      <c r="B36" s="58"/>
+      <c r="C36" s="57" t="s">
         <v>12</v>
       </c>
       <c r="D36" s="48" t="s">
@@ -2564,15 +2558,15 @@
         <v>98</v>
       </c>
       <c r="G36" s="21" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="37.5" x14ac:dyDescent="0.25">
       <c r="A37" s="9">
         <v>32</v>
       </c>
-      <c r="B37" s="58"/>
-      <c r="C37" s="59"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="57"/>
       <c r="D37" s="49" t="s">
         <v>99</v>
       </c>
@@ -2588,8 +2582,8 @@
       <c r="A38" s="9">
         <v>33</v>
       </c>
-      <c r="B38" s="57"/>
-      <c r="C38" s="59" t="s">
+      <c r="B38" s="58"/>
+      <c r="C38" s="57" t="s">
         <v>14</v>
       </c>
       <c r="D38" s="48" t="s">
@@ -2607,8 +2601,8 @@
       <c r="A39" s="9">
         <v>34</v>
       </c>
-      <c r="B39" s="58"/>
-      <c r="C39" s="59"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="57"/>
       <c r="D39" s="49" t="s">
         <v>103</v>
       </c>
@@ -2624,8 +2618,8 @@
       <c r="A40" s="9">
         <v>35</v>
       </c>
-      <c r="B40" s="57"/>
-      <c r="C40" s="59" t="s">
+      <c r="B40" s="58"/>
+      <c r="C40" s="57" t="s">
         <v>11</v>
       </c>
       <c r="D40" s="48" t="s">
@@ -2643,8 +2637,8 @@
       <c r="A41" s="9">
         <v>36</v>
       </c>
-      <c r="B41" s="58"/>
-      <c r="C41" s="59"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="57"/>
       <c r="D41" s="49" t="s">
         <v>107</v>
       </c>
@@ -2660,18 +2654,18 @@
       <c r="A42" s="9">
         <v>37</v>
       </c>
-      <c r="B42" s="57"/>
-      <c r="C42" s="67" t="s">
-        <v>110</v>
+      <c r="B42" s="58"/>
+      <c r="C42" s="61" t="s">
+        <v>109</v>
       </c>
       <c r="D42" s="51" t="s">
+        <v>122</v>
+      </c>
+      <c r="E42" s="27" t="s">
         <v>123</v>
       </c>
-      <c r="E42" s="27" t="s">
+      <c r="F42" s="28" t="s">
         <v>124</v>
-      </c>
-      <c r="F42" s="28" t="s">
-        <v>125</v>
       </c>
       <c r="G42" s="21"/>
     </row>
@@ -2679,16 +2673,16 @@
       <c r="A43" s="9">
         <v>38</v>
       </c>
-      <c r="B43" s="58"/>
-      <c r="C43" s="67"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="61"/>
       <c r="D43" s="50" t="s">
+        <v>125</v>
+      </c>
+      <c r="E43" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="E43" s="25" t="s">
+      <c r="F43" s="29" t="s">
         <v>127</v>
-      </c>
-      <c r="F43" s="29" t="s">
-        <v>128</v>
       </c>
       <c r="G43" s="24"/>
     </row>
@@ -2696,18 +2690,18 @@
       <c r="A44" s="9">
         <v>39</v>
       </c>
-      <c r="B44" s="57"/>
-      <c r="C44" s="59" t="s">
-        <v>111</v>
+      <c r="B44" s="58"/>
+      <c r="C44" s="57" t="s">
+        <v>110</v>
       </c>
       <c r="D44" s="51" t="s">
+        <v>128</v>
+      </c>
+      <c r="E44" s="27" t="s">
         <v>129</v>
       </c>
-      <c r="E44" s="27" t="s">
+      <c r="F44" s="30" t="s">
         <v>130</v>
-      </c>
-      <c r="F44" s="30" t="s">
-        <v>131</v>
       </c>
       <c r="G44" s="21"/>
     </row>
@@ -2715,16 +2709,16 @@
       <c r="A45" s="9">
         <v>40</v>
       </c>
-      <c r="B45" s="58"/>
-      <c r="C45" s="59"/>
+      <c r="B45" s="59"/>
+      <c r="C45" s="57"/>
       <c r="D45" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="E45" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="E45" s="25" t="s">
+      <c r="F45" s="29" t="s">
         <v>133</v>
-      </c>
-      <c r="F45" s="29" t="s">
-        <v>134</v>
       </c>
       <c r="G45" s="24"/>
     </row>
@@ -2732,18 +2726,18 @@
       <c r="A46" s="9">
         <v>41</v>
       </c>
-      <c r="B46" s="57"/>
-      <c r="C46" s="59" t="s">
-        <v>112</v>
+      <c r="B46" s="58"/>
+      <c r="C46" s="57" t="s">
+        <v>111</v>
       </c>
       <c r="D46" s="51" t="s">
+        <v>134</v>
+      </c>
+      <c r="E46" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F46" s="30" t="s">
         <v>135</v>
-      </c>
-      <c r="E46" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F46" s="30" t="s">
-        <v>136</v>
       </c>
       <c r="G46" s="21"/>
     </row>
@@ -2751,16 +2745,16 @@
       <c r="A47" s="9">
         <v>42</v>
       </c>
-      <c r="B47" s="58"/>
-      <c r="C47" s="59"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="57"/>
       <c r="D47" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F47" s="31" t="s">
         <v>137</v>
-      </c>
-      <c r="E47" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F47" s="31" t="s">
-        <v>138</v>
       </c>
       <c r="G47" s="24"/>
     </row>
@@ -2768,18 +2762,18 @@
       <c r="A48" s="9">
         <v>43</v>
       </c>
-      <c r="B48" s="57"/>
-      <c r="C48" s="59" t="s">
-        <v>113</v>
+      <c r="B48" s="58"/>
+      <c r="C48" s="57" t="s">
+        <v>112</v>
       </c>
       <c r="D48" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="E48" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F48" s="32" t="s">
         <v>139</v>
-      </c>
-      <c r="E48" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F48" s="32" t="s">
-        <v>140</v>
       </c>
       <c r="G48" s="21"/>
     </row>
@@ -2787,16 +2781,16 @@
       <c r="A49" s="9">
         <v>44</v>
       </c>
-      <c r="B49" s="58"/>
-      <c r="C49" s="59"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="57"/>
       <c r="D49" s="50" t="s">
+        <v>140</v>
+      </c>
+      <c r="E49" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F49" s="33" t="s">
         <v>141</v>
-      </c>
-      <c r="E49" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F49" s="33" t="s">
-        <v>142</v>
       </c>
       <c r="G49" s="24"/>
     </row>
@@ -2804,18 +2798,18 @@
       <c r="A50" s="9">
         <v>45</v>
       </c>
-      <c r="B50" s="57"/>
-      <c r="C50" s="64" t="s">
+      <c r="B50" s="58"/>
+      <c r="C50" s="60" t="s">
         <v>4</v>
       </c>
       <c r="D50" s="51" t="s">
+        <v>142</v>
+      </c>
+      <c r="E50" s="27" t="s">
         <v>143</v>
       </c>
-      <c r="E50" s="27" t="s">
+      <c r="F50" s="30" t="s">
         <v>144</v>
-      </c>
-      <c r="F50" s="30" t="s">
-        <v>145</v>
       </c>
       <c r="G50" s="21"/>
     </row>
@@ -2823,16 +2817,16 @@
       <c r="A51" s="9">
         <v>46</v>
       </c>
-      <c r="B51" s="58"/>
-      <c r="C51" s="64"/>
+      <c r="B51" s="59"/>
+      <c r="C51" s="60"/>
       <c r="D51" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="E51" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="E51" s="25" t="s">
+      <c r="F51" s="29" t="s">
         <v>147</v>
-      </c>
-      <c r="F51" s="29" t="s">
-        <v>148</v>
       </c>
       <c r="G51" s="24"/>
     </row>
@@ -2840,18 +2834,18 @@
       <c r="A52" s="9">
         <v>47</v>
       </c>
-      <c r="B52" s="57"/>
-      <c r="C52" s="59" t="s">
-        <v>114</v>
+      <c r="B52" s="58"/>
+      <c r="C52" s="57" t="s">
+        <v>113</v>
       </c>
       <c r="D52" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="E52" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F52" s="30" t="s">
         <v>149</v>
-      </c>
-      <c r="E52" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F52" s="30" t="s">
-        <v>150</v>
       </c>
       <c r="G52" s="21"/>
     </row>
@@ -2859,16 +2853,16 @@
       <c r="A53" s="9">
         <v>48</v>
       </c>
-      <c r="B53" s="58"/>
-      <c r="C53" s="59"/>
+      <c r="B53" s="59"/>
+      <c r="C53" s="57"/>
       <c r="D53" s="50" t="s">
+        <v>150</v>
+      </c>
+      <c r="E53" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="E53" s="25" t="s">
+      <c r="F53" s="29" t="s">
         <v>152</v>
-      </c>
-      <c r="F53" s="29" t="s">
-        <v>153</v>
       </c>
       <c r="G53" s="24"/>
     </row>
@@ -2876,18 +2870,18 @@
       <c r="A54" s="9">
         <v>49</v>
       </c>
-      <c r="B54" s="57"/>
-      <c r="C54" s="59" t="s">
-        <v>115</v>
+      <c r="B54" s="58"/>
+      <c r="C54" s="57" t="s">
+        <v>114</v>
       </c>
       <c r="D54" s="51" t="s">
+        <v>153</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F54" s="30" t="s">
         <v>154</v>
-      </c>
-      <c r="E54" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F54" s="30" t="s">
-        <v>155</v>
       </c>
       <c r="G54" s="21"/>
     </row>
@@ -2895,16 +2889,16 @@
       <c r="A55" s="9">
         <v>50</v>
       </c>
-      <c r="B55" s="58"/>
-      <c r="C55" s="59"/>
+      <c r="B55" s="59"/>
+      <c r="C55" s="57"/>
       <c r="D55" s="50" t="s">
+        <v>155</v>
+      </c>
+      <c r="E55" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F55" s="34" t="s">
         <v>156</v>
-      </c>
-      <c r="E55" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F55" s="34" t="s">
-        <v>157</v>
       </c>
       <c r="G55" s="24"/>
     </row>
@@ -2912,18 +2906,18 @@
       <c r="A56" s="9">
         <v>51</v>
       </c>
-      <c r="B56" s="57"/>
-      <c r="C56" s="59" t="s">
-        <v>116</v>
+      <c r="B56" s="58"/>
+      <c r="C56" s="57" t="s">
+        <v>115</v>
       </c>
       <c r="D56" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F56" s="28" t="s">
         <v>158</v>
-      </c>
-      <c r="E56" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F56" s="28" t="s">
-        <v>159</v>
       </c>
       <c r="G56" s="21"/>
     </row>
@@ -2931,16 +2925,16 @@
       <c r="A57" s="9">
         <v>52</v>
       </c>
-      <c r="B57" s="58"/>
-      <c r="C57" s="59"/>
+      <c r="B57" s="59"/>
+      <c r="C57" s="57"/>
       <c r="D57" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="E57" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F57" s="34" t="s">
         <v>160</v>
-      </c>
-      <c r="E57" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F57" s="34" t="s">
-        <v>161</v>
       </c>
       <c r="G57" s="24"/>
     </row>
@@ -2948,18 +2942,18 @@
       <c r="A58" s="9">
         <v>53</v>
       </c>
-      <c r="B58" s="57"/>
-      <c r="C58" s="59" t="s">
-        <v>117</v>
+      <c r="B58" s="58"/>
+      <c r="C58" s="57" t="s">
+        <v>116</v>
       </c>
       <c r="D58" s="51" t="s">
+        <v>161</v>
+      </c>
+      <c r="E58" s="27" t="s">
         <v>162</v>
       </c>
-      <c r="E58" s="27" t="s">
+      <c r="F58" s="30" t="s">
         <v>163</v>
-      </c>
-      <c r="F58" s="30" t="s">
-        <v>164</v>
       </c>
       <c r="G58" s="21"/>
     </row>
@@ -2967,16 +2961,16 @@
       <c r="A59" s="9">
         <v>54</v>
       </c>
-      <c r="B59" s="58"/>
-      <c r="C59" s="59"/>
+      <c r="B59" s="59"/>
+      <c r="C59" s="57"/>
       <c r="D59" s="50" t="s">
+        <v>164</v>
+      </c>
+      <c r="E59" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F59" s="34" t="s">
         <v>165</v>
-      </c>
-      <c r="E59" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F59" s="34" t="s">
-        <v>166</v>
       </c>
       <c r="G59" s="24"/>
     </row>
@@ -2984,18 +2978,18 @@
       <c r="A60" s="9">
         <v>55</v>
       </c>
-      <c r="B60" s="57"/>
-      <c r="C60" s="59" t="s">
-        <v>118</v>
+      <c r="B60" s="58"/>
+      <c r="C60" s="57" t="s">
+        <v>117</v>
       </c>
       <c r="D60" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="E60" s="27" t="s">
         <v>167</v>
       </c>
-      <c r="E60" s="27" t="s">
+      <c r="F60" s="30" t="s">
         <v>168</v>
-      </c>
-      <c r="F60" s="30" t="s">
-        <v>169</v>
       </c>
       <c r="G60" s="21"/>
       <c r="I60" s="1"/>
@@ -3006,16 +3000,16 @@
       <c r="A61" s="9">
         <v>56</v>
       </c>
-      <c r="B61" s="58"/>
-      <c r="C61" s="59"/>
+      <c r="B61" s="59"/>
+      <c r="C61" s="57"/>
       <c r="D61" s="50" t="s">
+        <v>169</v>
+      </c>
+      <c r="E61" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F61" s="34" t="s">
         <v>170</v>
-      </c>
-      <c r="E61" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F61" s="34" t="s">
-        <v>171</v>
       </c>
       <c r="G61" s="24"/>
       <c r="I61" s="1"/>
@@ -3026,18 +3020,18 @@
       <c r="A62" s="9">
         <v>57</v>
       </c>
-      <c r="B62" s="57"/>
-      <c r="C62" s="59" t="s">
-        <v>119</v>
+      <c r="B62" s="58"/>
+      <c r="C62" s="57" t="s">
+        <v>118</v>
       </c>
       <c r="D62" s="51" t="s">
+        <v>171</v>
+      </c>
+      <c r="E62" s="27" t="s">
+        <v>143</v>
+      </c>
+      <c r="F62" s="28" t="s">
         <v>172</v>
-      </c>
-      <c r="E62" s="27" t="s">
-        <v>144</v>
-      </c>
-      <c r="F62" s="28" t="s">
-        <v>173</v>
       </c>
       <c r="G62" s="21"/>
       <c r="I62" s="1"/>
@@ -3048,16 +3042,16 @@
       <c r="A63" s="9">
         <v>58</v>
       </c>
-      <c r="B63" s="58"/>
-      <c r="C63" s="59"/>
+      <c r="B63" s="59"/>
+      <c r="C63" s="57"/>
       <c r="D63" s="50" t="s">
+        <v>173</v>
+      </c>
+      <c r="E63" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="E63" s="25" t="s">
+      <c r="F63" s="29" t="s">
         <v>175</v>
-      </c>
-      <c r="F63" s="29" t="s">
-        <v>176</v>
       </c>
       <c r="G63" s="24"/>
       <c r="I63" s="1"/>
@@ -3068,18 +3062,18 @@
       <c r="A64" s="9">
         <v>59</v>
       </c>
-      <c r="B64" s="65"/>
-      <c r="C64" s="64" t="s">
-        <v>120</v>
+      <c r="B64" s="62"/>
+      <c r="C64" s="60" t="s">
+        <v>119</v>
       </c>
       <c r="D64" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="E64" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F64" s="32" t="s">
         <v>177</v>
-      </c>
-      <c r="E64" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F64" s="32" t="s">
-        <v>178</v>
       </c>
       <c r="G64" s="21"/>
     </row>
@@ -3087,16 +3081,16 @@
       <c r="A65" s="9">
         <v>60</v>
       </c>
-      <c r="B65" s="66"/>
-      <c r="C65" s="64"/>
+      <c r="B65" s="63"/>
+      <c r="C65" s="60"/>
       <c r="D65" s="50" t="s">
+        <v>178</v>
+      </c>
+      <c r="E65" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F65" s="33" t="s">
         <v>179</v>
-      </c>
-      <c r="E65" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F65" s="33" t="s">
-        <v>180</v>
       </c>
       <c r="G65" s="24"/>
     </row>
@@ -3104,18 +3098,18 @@
       <c r="A66" s="9">
         <v>61</v>
       </c>
-      <c r="B66" s="57"/>
-      <c r="C66" s="59" t="s">
-        <v>121</v>
+      <c r="B66" s="58"/>
+      <c r="C66" s="57" t="s">
+        <v>120</v>
       </c>
       <c r="D66" s="51" t="s">
+        <v>180</v>
+      </c>
+      <c r="E66" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F66" s="30" t="s">
         <v>181</v>
-      </c>
-      <c r="E66" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F66" s="30" t="s">
-        <v>182</v>
       </c>
       <c r="G66" s="21"/>
     </row>
@@ -3123,16 +3117,16 @@
       <c r="A67" s="9">
         <v>62</v>
       </c>
-      <c r="B67" s="58"/>
-      <c r="C67" s="59"/>
+      <c r="B67" s="59"/>
+      <c r="C67" s="57"/>
       <c r="D67" s="50" t="s">
+        <v>182</v>
+      </c>
+      <c r="E67" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F67" s="29" t="s">
         <v>183</v>
-      </c>
-      <c r="E67" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F67" s="29" t="s">
-        <v>184</v>
       </c>
       <c r="G67" s="24"/>
     </row>
@@ -3140,18 +3134,18 @@
       <c r="A68" s="9">
         <v>63</v>
       </c>
-      <c r="B68" s="57"/>
-      <c r="C68" s="59" t="s">
-        <v>122</v>
+      <c r="B68" s="58"/>
+      <c r="C68" s="57" t="s">
+        <v>121</v>
       </c>
       <c r="D68" s="51" t="s">
+        <v>184</v>
+      </c>
+      <c r="E68" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="E68" s="27" t="s">
+      <c r="F68" s="30" t="s">
         <v>186</v>
-      </c>
-      <c r="F68" s="30" t="s">
-        <v>187</v>
       </c>
       <c r="G68" s="21"/>
     </row>
@@ -3159,16 +3153,16 @@
       <c r="A69" s="9">
         <v>64</v>
       </c>
-      <c r="B69" s="58"/>
-      <c r="C69" s="59"/>
+      <c r="B69" s="59"/>
+      <c r="C69" s="57"/>
       <c r="D69" s="50" t="s">
+        <v>187</v>
+      </c>
+      <c r="E69" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="F69" s="29" t="s">
         <v>188</v>
-      </c>
-      <c r="E69" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="F69" s="29" t="s">
-        <v>189</v>
       </c>
       <c r="G69" s="24"/>
     </row>
@@ -3176,18 +3170,18 @@
       <c r="A70" s="9">
         <v>65</v>
       </c>
-      <c r="B70" s="57"/>
-      <c r="C70" s="59" t="s">
+      <c r="B70" s="58"/>
+      <c r="C70" s="57" t="s">
         <v>5</v>
       </c>
       <c r="D70" s="51" t="s">
+        <v>189</v>
+      </c>
+      <c r="E70" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F70" s="28" t="s">
         <v>190</v>
-      </c>
-      <c r="E70" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F70" s="28" t="s">
-        <v>191</v>
       </c>
       <c r="G70" s="21"/>
     </row>
@@ -3195,16 +3189,16 @@
       <c r="A71" s="9">
         <v>66</v>
       </c>
-      <c r="B71" s="58"/>
-      <c r="C71" s="59"/>
+      <c r="B71" s="59"/>
+      <c r="C71" s="57"/>
       <c r="D71" s="50" t="s">
+        <v>191</v>
+      </c>
+      <c r="E71" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="E71" s="25" t="s">
+      <c r="F71" s="29" t="s">
         <v>193</v>
-      </c>
-      <c r="F71" s="29" t="s">
-        <v>194</v>
       </c>
       <c r="G71" s="24"/>
     </row>
@@ -3212,18 +3206,18 @@
       <c r="A72" s="9">
         <v>67</v>
       </c>
-      <c r="B72" s="57"/>
-      <c r="C72" s="59" t="s">
-        <v>195</v>
+      <c r="B72" s="58"/>
+      <c r="C72" s="57" t="s">
+        <v>194</v>
       </c>
       <c r="D72" s="48" t="s">
+        <v>212</v>
+      </c>
+      <c r="E72" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F72" s="35" t="s">
         <v>213</v>
-      </c>
-      <c r="E72" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F72" s="35" t="s">
-        <v>214</v>
       </c>
       <c r="G72" s="21"/>
     </row>
@@ -3231,16 +3225,16 @@
       <c r="A73" s="9">
         <v>68</v>
       </c>
-      <c r="B73" s="58"/>
-      <c r="C73" s="59"/>
+      <c r="B73" s="59"/>
+      <c r="C73" s="57"/>
       <c r="D73" s="52" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E73" s="25" t="s">
         <v>37</v>
       </c>
       <c r="F73" s="36" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G73" s="24"/>
     </row>
@@ -3248,18 +3242,18 @@
       <c r="A74" s="9">
         <v>69</v>
       </c>
-      <c r="B74" s="57"/>
-      <c r="C74" s="59" t="s">
-        <v>196</v>
+      <c r="B74" s="58"/>
+      <c r="C74" s="57" t="s">
+        <v>195</v>
       </c>
       <c r="D74" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="E74" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F74" s="37" t="s">
         <v>215</v>
-      </c>
-      <c r="E74" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F74" s="37" t="s">
-        <v>216</v>
       </c>
       <c r="G74" s="38"/>
       <c r="I74" s="3"/>
@@ -3268,16 +3262,16 @@
       <c r="A75" s="9">
         <v>70</v>
       </c>
-      <c r="B75" s="58"/>
-      <c r="C75" s="59"/>
+      <c r="B75" s="59"/>
+      <c r="C75" s="57"/>
       <c r="D75" s="52" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E75" s="25" t="s">
         <v>37</v>
       </c>
       <c r="F75" s="36" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G75" s="39"/>
       <c r="I75" s="4"/>
@@ -3288,16 +3282,16 @@
       </c>
       <c r="B76" s="14"/>
       <c r="C76" s="56" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D76" s="53" t="s">
+        <v>216</v>
+      </c>
+      <c r="E76" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F76" s="18" t="s">
         <v>217</v>
-      </c>
-      <c r="E76" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="F76" s="18" t="s">
-        <v>218</v>
       </c>
       <c r="G76" s="10"/>
     </row>
@@ -3305,18 +3299,18 @@
       <c r="A77" s="9">
         <v>72</v>
       </c>
-      <c r="B77" s="57"/>
-      <c r="C77" s="59" t="s">
-        <v>198</v>
+      <c r="B77" s="58"/>
+      <c r="C77" s="57" t="s">
+        <v>197</v>
       </c>
       <c r="D77" s="48" t="s">
+        <v>218</v>
+      </c>
+      <c r="E77" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F77" s="37" t="s">
         <v>219</v>
-      </c>
-      <c r="E77" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F77" s="37" t="s">
-        <v>220</v>
       </c>
       <c r="G77" s="21"/>
     </row>
@@ -3324,16 +3318,16 @@
       <c r="A78" s="9">
         <v>73</v>
       </c>
-      <c r="B78" s="58"/>
-      <c r="C78" s="59"/>
+      <c r="B78" s="59"/>
+      <c r="C78" s="57"/>
       <c r="D78" s="52" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E78" s="25" t="s">
         <v>37</v>
       </c>
       <c r="F78" s="36" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G78" s="24"/>
     </row>
@@ -3341,18 +3335,18 @@
       <c r="A79" s="9">
         <v>74</v>
       </c>
-      <c r="B79" s="57"/>
-      <c r="C79" s="59" t="s">
-        <v>199</v>
+      <c r="B79" s="58"/>
+      <c r="C79" s="57" t="s">
+        <v>198</v>
       </c>
       <c r="D79" s="48" t="s">
+        <v>220</v>
+      </c>
+      <c r="E79" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F79" s="40" t="s">
         <v>221</v>
-      </c>
-      <c r="E79" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F79" s="40" t="s">
-        <v>222</v>
       </c>
       <c r="G79" s="21"/>
     </row>
@@ -3360,16 +3354,16 @@
       <c r="A80" s="9">
         <v>75</v>
       </c>
-      <c r="B80" s="58"/>
-      <c r="C80" s="59"/>
+      <c r="B80" s="59"/>
+      <c r="C80" s="57"/>
       <c r="D80" s="52" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E80" s="25" t="s">
         <v>37</v>
       </c>
       <c r="F80" s="36" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G80" s="24"/>
     </row>
@@ -3377,18 +3371,18 @@
       <c r="A81" s="9">
         <v>76</v>
       </c>
-      <c r="B81" s="57"/>
-      <c r="C81" s="59" t="s">
-        <v>200</v>
+      <c r="B81" s="58"/>
+      <c r="C81" s="57" t="s">
+        <v>199</v>
       </c>
       <c r="D81" s="48" t="s">
+        <v>222</v>
+      </c>
+      <c r="E81" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F81" s="37" t="s">
         <v>223</v>
-      </c>
-      <c r="E81" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F81" s="37" t="s">
-        <v>224</v>
       </c>
       <c r="G81" s="21"/>
     </row>
@@ -3396,16 +3390,16 @@
       <c r="A82" s="9">
         <v>77</v>
       </c>
-      <c r="B82" s="58"/>
-      <c r="C82" s="59"/>
+      <c r="B82" s="59"/>
+      <c r="C82" s="57"/>
       <c r="D82" s="52" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="E82" s="25" t="s">
         <v>37</v>
       </c>
       <c r="F82" s="36" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G82" s="24"/>
     </row>
@@ -3413,18 +3407,18 @@
       <c r="A83" s="9">
         <v>78</v>
       </c>
-      <c r="B83" s="57"/>
-      <c r="C83" s="59" t="s">
-        <v>201</v>
+      <c r="B83" s="58"/>
+      <c r="C83" s="57" t="s">
+        <v>200</v>
       </c>
       <c r="D83" s="48" t="s">
+        <v>224</v>
+      </c>
+      <c r="E83" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F83" s="41" t="s">
         <v>225</v>
-      </c>
-      <c r="E83" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F83" s="41" t="s">
-        <v>226</v>
       </c>
       <c r="G83" s="21"/>
     </row>
@@ -3432,16 +3426,16 @@
       <c r="A84" s="9">
         <v>79</v>
       </c>
-      <c r="B84" s="58"/>
-      <c r="C84" s="59"/>
+      <c r="B84" s="59"/>
+      <c r="C84" s="57"/>
       <c r="D84" s="52" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E84" s="25" t="s">
         <v>37</v>
       </c>
       <c r="F84" s="36" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G84" s="24"/>
     </row>
@@ -3449,18 +3443,18 @@
       <c r="A85" s="9">
         <v>80</v>
       </c>
-      <c r="B85" s="57"/>
-      <c r="C85" s="59" t="s">
-        <v>202</v>
+      <c r="B85" s="58"/>
+      <c r="C85" s="57" t="s">
+        <v>201</v>
       </c>
       <c r="D85" s="48" t="s">
+        <v>226</v>
+      </c>
+      <c r="E85" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F85" s="37" t="s">
         <v>227</v>
-      </c>
-      <c r="E85" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F85" s="37" t="s">
-        <v>228</v>
       </c>
       <c r="G85" s="21"/>
     </row>
@@ -3468,16 +3462,16 @@
       <c r="A86" s="9">
         <v>81</v>
       </c>
-      <c r="B86" s="58"/>
-      <c r="C86" s="59"/>
+      <c r="B86" s="59"/>
+      <c r="C86" s="57"/>
       <c r="D86" s="52" t="s">
+        <v>264</v>
+      </c>
+      <c r="E86" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="F86" s="36" t="s">
         <v>265</v>
-      </c>
-      <c r="E86" s="25" t="s">
-        <v>287</v>
-      </c>
-      <c r="F86" s="36" t="s">
-        <v>266</v>
       </c>
       <c r="G86" s="42"/>
     </row>
@@ -3485,18 +3479,18 @@
       <c r="A87" s="9">
         <v>82</v>
       </c>
-      <c r="B87" s="57"/>
-      <c r="C87" s="59" t="s">
-        <v>203</v>
+      <c r="B87" s="58"/>
+      <c r="C87" s="57" t="s">
+        <v>202</v>
       </c>
       <c r="D87" s="48" t="s">
+        <v>228</v>
+      </c>
+      <c r="E87" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F87" s="40" t="s">
         <v>229</v>
-      </c>
-      <c r="E87" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F87" s="40" t="s">
-        <v>230</v>
       </c>
       <c r="G87" s="21"/>
     </row>
@@ -3504,16 +3498,16 @@
       <c r="A88" s="9">
         <v>83</v>
       </c>
-      <c r="B88" s="58"/>
-      <c r="C88" s="59"/>
+      <c r="B88" s="59"/>
+      <c r="C88" s="57"/>
       <c r="D88" s="52" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E88" s="25" t="s">
         <v>37</v>
       </c>
       <c r="F88" s="43" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G88" s="24"/>
     </row>
@@ -3521,18 +3515,18 @@
       <c r="A89" s="9">
         <v>84</v>
       </c>
-      <c r="B89" s="57"/>
-      <c r="C89" s="59" t="s">
+      <c r="B89" s="58"/>
+      <c r="C89" s="57" t="s">
         <v>6</v>
       </c>
       <c r="D89" s="48" t="s">
+        <v>230</v>
+      </c>
+      <c r="E89" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F89" s="37" t="s">
         <v>231</v>
-      </c>
-      <c r="E89" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F89" s="37" t="s">
-        <v>232</v>
       </c>
       <c r="G89" s="21"/>
     </row>
@@ -3540,16 +3534,16 @@
       <c r="A90" s="9">
         <v>85</v>
       </c>
-      <c r="B90" s="58"/>
-      <c r="C90" s="59"/>
+      <c r="B90" s="59"/>
+      <c r="C90" s="57"/>
       <c r="D90" s="52" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E90" s="25" t="s">
         <v>37</v>
       </c>
       <c r="F90" s="36" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G90" s="24"/>
     </row>
@@ -3559,16 +3553,16 @@
       </c>
       <c r="B91" s="14"/>
       <c r="C91" s="56" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D91" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F91" s="18" t="s">
         <v>233</v>
-      </c>
-      <c r="E91" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="F91" s="18" t="s">
-        <v>234</v>
       </c>
       <c r="G91" s="10"/>
     </row>
@@ -3576,37 +3570,37 @@
       <c r="A92" s="9">
         <v>87</v>
       </c>
-      <c r="B92" s="57"/>
-      <c r="C92" s="59" t="s">
-        <v>205</v>
+      <c r="B92" s="58"/>
+      <c r="C92" s="57" t="s">
+        <v>204</v>
       </c>
       <c r="D92" s="48" t="s">
+        <v>234</v>
+      </c>
+      <c r="E92" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F92" s="40" t="s">
         <v>235</v>
       </c>
-      <c r="E92" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F92" s="40" t="s">
-        <v>236</v>
-      </c>
       <c r="G92" s="44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="9">
         <v>88</v>
       </c>
-      <c r="B93" s="58"/>
-      <c r="C93" s="59"/>
+      <c r="B93" s="59"/>
+      <c r="C93" s="57"/>
       <c r="D93" s="52" t="s">
+        <v>270</v>
+      </c>
+      <c r="E93" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="F93" s="43" t="s">
         <v>271</v>
-      </c>
-      <c r="E93" s="25" t="s">
-        <v>287</v>
-      </c>
-      <c r="F93" s="43" t="s">
-        <v>272</v>
       </c>
       <c r="G93" s="42"/>
     </row>
@@ -3614,18 +3608,18 @@
       <c r="A94" s="9">
         <v>89</v>
       </c>
-      <c r="B94" s="57"/>
-      <c r="C94" s="59" t="s">
-        <v>206</v>
+      <c r="B94" s="58"/>
+      <c r="C94" s="57" t="s">
+        <v>205</v>
       </c>
       <c r="D94" s="48" t="s">
+        <v>236</v>
+      </c>
+      <c r="E94" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F94" s="37" t="s">
         <v>237</v>
-      </c>
-      <c r="E94" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F94" s="37" t="s">
-        <v>238</v>
       </c>
       <c r="G94" s="21"/>
     </row>
@@ -3633,16 +3627,16 @@
       <c r="A95" s="9">
         <v>90</v>
       </c>
-      <c r="B95" s="58"/>
-      <c r="C95" s="59"/>
+      <c r="B95" s="59"/>
+      <c r="C95" s="57"/>
       <c r="D95" s="52" t="s">
+        <v>272</v>
+      </c>
+      <c r="E95" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="F95" s="36" t="s">
         <v>273</v>
-      </c>
-      <c r="E95" s="25" t="s">
-        <v>286</v>
-      </c>
-      <c r="F95" s="36" t="s">
-        <v>274</v>
       </c>
       <c r="G95" s="42"/>
     </row>
@@ -3650,37 +3644,37 @@
       <c r="A96" s="9">
         <v>91</v>
       </c>
-      <c r="B96" s="57"/>
-      <c r="C96" s="59" t="s">
-        <v>207</v>
+      <c r="B96" s="58"/>
+      <c r="C96" s="57" t="s">
+        <v>206</v>
       </c>
       <c r="D96" s="48" t="s">
+        <v>238</v>
+      </c>
+      <c r="E96" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F96" s="40" t="s">
         <v>239</v>
       </c>
-      <c r="E96" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F96" s="40" t="s">
-        <v>240</v>
-      </c>
       <c r="G96" s="44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="9">
         <v>92</v>
       </c>
-      <c r="B97" s="58"/>
-      <c r="C97" s="59"/>
+      <c r="B97" s="59"/>
+      <c r="C97" s="57"/>
       <c r="D97" s="52" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E97" s="25" t="s">
         <v>37</v>
       </c>
       <c r="F97" s="36" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G97" s="42"/>
     </row>
@@ -3688,37 +3682,37 @@
       <c r="A98" s="9">
         <v>93</v>
       </c>
-      <c r="B98" s="57"/>
-      <c r="C98" s="59" t="s">
-        <v>208</v>
+      <c r="B98" s="58"/>
+      <c r="C98" s="57" t="s">
+        <v>207</v>
       </c>
       <c r="D98" s="48" t="s">
+        <v>240</v>
+      </c>
+      <c r="E98" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F98" s="40" t="s">
         <v>241</v>
       </c>
-      <c r="E98" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F98" s="40" t="s">
-        <v>242</v>
-      </c>
       <c r="G98" s="44" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>94</v>
       </c>
-      <c r="B99" s="58"/>
-      <c r="C99" s="59"/>
+      <c r="B99" s="59"/>
+      <c r="C99" s="57"/>
       <c r="D99" s="52" t="s">
+        <v>276</v>
+      </c>
+      <c r="E99" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="F99" s="36" t="s">
         <v>277</v>
-      </c>
-      <c r="E99" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="F99" s="36" t="s">
-        <v>278</v>
       </c>
       <c r="G99" s="42"/>
     </row>
@@ -3726,18 +3720,18 @@
       <c r="A100" s="9">
         <v>95</v>
       </c>
-      <c r="B100" s="65"/>
-      <c r="C100" s="64" t="s">
-        <v>209</v>
+      <c r="B100" s="62"/>
+      <c r="C100" s="60" t="s">
+        <v>208</v>
       </c>
       <c r="D100" s="48" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E100" s="27" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F100" s="37" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G100" s="21"/>
     </row>
@@ -3745,16 +3739,16 @@
       <c r="A101" s="9">
         <v>96</v>
       </c>
-      <c r="B101" s="66"/>
-      <c r="C101" s="64"/>
+      <c r="B101" s="63"/>
+      <c r="C101" s="60"/>
       <c r="D101" s="52" t="s">
+        <v>278</v>
+      </c>
+      <c r="E101" s="25" t="s">
+        <v>284</v>
+      </c>
+      <c r="F101" s="36" t="s">
         <v>279</v>
-      </c>
-      <c r="E101" s="25" t="s">
-        <v>285</v>
-      </c>
-      <c r="F101" s="36" t="s">
-        <v>280</v>
       </c>
       <c r="G101" s="42"/>
     </row>
@@ -3764,16 +3758,16 @@
       </c>
       <c r="B102" s="14"/>
       <c r="C102" s="56" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D102" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="E102" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="F102" s="17" t="s">
         <v>245</v>
-      </c>
-      <c r="E102" s="11" t="s">
-        <v>251</v>
-      </c>
-      <c r="F102" s="17" t="s">
-        <v>246</v>
       </c>
       <c r="G102" s="12"/>
     </row>
@@ -3781,18 +3775,18 @@
       <c r="A103" s="9">
         <v>98</v>
       </c>
-      <c r="B103" s="57"/>
-      <c r="C103" s="59" t="s">
-        <v>211</v>
+      <c r="B103" s="58"/>
+      <c r="C103" s="57" t="s">
+        <v>210</v>
       </c>
       <c r="D103" s="48" t="s">
+        <v>246</v>
+      </c>
+      <c r="E103" s="27" t="s">
+        <v>123</v>
+      </c>
+      <c r="F103" s="37" t="s">
         <v>247</v>
-      </c>
-      <c r="E103" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="F103" s="37" t="s">
-        <v>248</v>
       </c>
       <c r="G103" s="21"/>
     </row>
@@ -3800,16 +3794,16 @@
       <c r="A104" s="9">
         <v>99</v>
       </c>
-      <c r="B104" s="58"/>
-      <c r="C104" s="59"/>
+      <c r="B104" s="59"/>
+      <c r="C104" s="57"/>
       <c r="D104" s="52" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="E104" s="25" t="s">
         <v>37</v>
       </c>
       <c r="F104" s="36" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G104" s="24"/>
     </row>
@@ -3817,18 +3811,18 @@
       <c r="A105" s="9">
         <v>100</v>
       </c>
-      <c r="B105" s="57"/>
-      <c r="C105" s="59" t="s">
-        <v>212</v>
+      <c r="B105" s="58"/>
+      <c r="C105" s="57" t="s">
+        <v>211</v>
       </c>
       <c r="D105" s="48" t="s">
+        <v>248</v>
+      </c>
+      <c r="E105" s="27" t="s">
+        <v>251</v>
+      </c>
+      <c r="F105" s="41" t="s">
         <v>249</v>
-      </c>
-      <c r="E105" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="F105" s="41" t="s">
-        <v>250</v>
       </c>
       <c r="G105" s="44"/>
     </row>
@@ -3836,16 +3830,16 @@
       <c r="A106" s="9">
         <v>101</v>
       </c>
-      <c r="B106" s="58"/>
-      <c r="C106" s="59"/>
+      <c r="B106" s="59"/>
+      <c r="C106" s="57"/>
       <c r="D106" s="52" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E106" s="24" t="s">
         <v>37</v>
       </c>
       <c r="F106" s="36" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G106" s="24"/>
     </row>
@@ -3853,18 +3847,18 @@
       <c r="A107" s="9">
         <v>102</v>
       </c>
-      <c r="B107" s="57"/>
-      <c r="C107" s="59" t="s">
+      <c r="B107" s="58"/>
+      <c r="C107" s="57" t="s">
         <v>7</v>
       </c>
       <c r="D107" s="51" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E107" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F107" s="45" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G107" s="21"/>
     </row>
@@ -3872,16 +3866,16 @@
       <c r="A108" s="9">
         <v>103</v>
       </c>
-      <c r="B108" s="58"/>
-      <c r="C108" s="59"/>
+      <c r="B108" s="59"/>
+      <c r="C108" s="57"/>
       <c r="D108" s="50" t="s">
+        <v>309</v>
+      </c>
+      <c r="E108" s="22" t="s">
         <v>310</v>
       </c>
-      <c r="E108" s="22" t="s">
-        <v>311</v>
-      </c>
       <c r="F108" s="26" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G108" s="24"/>
     </row>
@@ -3889,18 +3883,18 @@
       <c r="A109" s="9">
         <v>104</v>
       </c>
-      <c r="B109" s="57"/>
-      <c r="C109" s="59" t="s">
-        <v>289</v>
+      <c r="B109" s="58"/>
+      <c r="C109" s="57" t="s">
+        <v>288</v>
       </c>
       <c r="D109" s="51" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E109" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F109" s="45" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="G109" s="21"/>
     </row>
@@ -3908,16 +3902,16 @@
       <c r="A110" s="9">
         <v>105</v>
       </c>
-      <c r="B110" s="58"/>
-      <c r="C110" s="59"/>
+      <c r="B110" s="59"/>
+      <c r="C110" s="57"/>
       <c r="D110" s="50" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="E110" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="G110" s="24"/>
     </row>
@@ -3927,16 +3921,16 @@
       </c>
       <c r="B111" s="14"/>
       <c r="C111" s="56" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D111" s="54" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F111" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="G111" s="10"/>
     </row>
@@ -3944,18 +3938,18 @@
       <c r="A112" s="9">
         <v>107</v>
       </c>
-      <c r="B112" s="57"/>
-      <c r="C112" s="59" t="s">
-        <v>291</v>
+      <c r="B112" s="58"/>
+      <c r="C112" s="57" t="s">
+        <v>290</v>
       </c>
       <c r="D112" s="51" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E112" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F112" s="45" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="G112" s="21"/>
     </row>
@@ -3963,16 +3957,16 @@
       <c r="A113" s="9">
         <v>108</v>
       </c>
-      <c r="B113" s="58"/>
-      <c r="C113" s="59"/>
+      <c r="B113" s="59"/>
+      <c r="C113" s="57"/>
       <c r="D113" s="50" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E113" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="G113" s="24"/>
     </row>
@@ -3980,18 +3974,18 @@
       <c r="A114" s="9">
         <v>109</v>
       </c>
-      <c r="B114" s="57"/>
-      <c r="C114" s="59" t="s">
-        <v>292</v>
+      <c r="B114" s="58"/>
+      <c r="C114" s="57" t="s">
+        <v>291</v>
       </c>
       <c r="D114" s="51" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E114" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F114" s="45" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="G114" s="21"/>
     </row>
@@ -3999,16 +3993,16 @@
       <c r="A115" s="9">
         <v>110</v>
       </c>
-      <c r="B115" s="58"/>
-      <c r="C115" s="59"/>
+      <c r="B115" s="59"/>
+      <c r="C115" s="57"/>
       <c r="D115" s="50" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E115" s="22" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G115" s="24"/>
     </row>
@@ -4018,16 +4012,16 @@
       </c>
       <c r="B116" s="14"/>
       <c r="C116" s="56" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D116" s="54" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F116" s="13" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G116" s="10"/>
     </row>
@@ -4035,18 +4029,18 @@
       <c r="A117" s="9">
         <v>112</v>
       </c>
-      <c r="B117" s="57"/>
-      <c r="C117" s="59" t="s">
-        <v>294</v>
+      <c r="B117" s="58"/>
+      <c r="C117" s="57" t="s">
+        <v>293</v>
       </c>
       <c r="D117" s="51" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E117" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F117" s="45" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="G117" s="21"/>
     </row>
@@ -4054,16 +4048,16 @@
       <c r="A118" s="9">
         <v>113</v>
       </c>
-      <c r="B118" s="58"/>
-      <c r="C118" s="59"/>
+      <c r="B118" s="59"/>
+      <c r="C118" s="57"/>
       <c r="D118" s="50" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E118" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F118" s="26" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="G118" s="24"/>
     </row>
@@ -4071,18 +4065,18 @@
       <c r="A119" s="9">
         <v>114</v>
       </c>
-      <c r="B119" s="57"/>
-      <c r="C119" s="59" t="s">
-        <v>295</v>
+      <c r="B119" s="58"/>
+      <c r="C119" s="57" t="s">
+        <v>294</v>
       </c>
       <c r="D119" s="51" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E119" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F119" s="45" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="G119" s="21"/>
     </row>
@@ -4090,16 +4084,16 @@
       <c r="A120" s="9">
         <v>115</v>
       </c>
-      <c r="B120" s="58"/>
-      <c r="C120" s="59"/>
+      <c r="B120" s="59"/>
+      <c r="C120" s="57"/>
       <c r="D120" s="50" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E120" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F120" s="26" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G120" s="24"/>
     </row>
@@ -4107,18 +4101,18 @@
       <c r="A121" s="9">
         <v>116</v>
       </c>
-      <c r="B121" s="57"/>
-      <c r="C121" s="59" t="s">
-        <v>296</v>
+      <c r="B121" s="58"/>
+      <c r="C121" s="57" t="s">
+        <v>295</v>
       </c>
       <c r="D121" s="51" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E121" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F121" s="45" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G121" s="21"/>
     </row>
@@ -4126,16 +4120,16 @@
       <c r="A122" s="9">
         <v>117</v>
       </c>
-      <c r="B122" s="58"/>
-      <c r="C122" s="59"/>
+      <c r="B122" s="59"/>
+      <c r="C122" s="57"/>
       <c r="D122" s="50" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="E122" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G122" s="24"/>
     </row>
@@ -4143,18 +4137,18 @@
       <c r="A123" s="9">
         <v>118</v>
       </c>
-      <c r="B123" s="57"/>
-      <c r="C123" s="59" t="s">
-        <v>297</v>
+      <c r="B123" s="58"/>
+      <c r="C123" s="57" t="s">
+        <v>296</v>
       </c>
       <c r="D123" s="51" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="E123" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F123" s="45" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G123" s="21"/>
     </row>
@@ -4162,16 +4156,16 @@
       <c r="A124" s="9">
         <v>119</v>
       </c>
-      <c r="B124" s="58"/>
-      <c r="C124" s="59"/>
+      <c r="B124" s="59"/>
+      <c r="C124" s="57"/>
       <c r="D124" s="50" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E124" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G124" s="24"/>
     </row>
@@ -4179,18 +4173,18 @@
       <c r="A125" s="9">
         <v>120</v>
       </c>
-      <c r="B125" s="57"/>
-      <c r="C125" s="59" t="s">
+      <c r="B125" s="58"/>
+      <c r="C125" s="57" t="s">
         <v>8</v>
       </c>
       <c r="D125" s="51" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E125" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F125" s="45" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G125" s="21"/>
     </row>
@@ -4198,16 +4192,16 @@
       <c r="A126" s="9">
         <v>121</v>
       </c>
-      <c r="B126" s="58"/>
-      <c r="C126" s="59"/>
+      <c r="B126" s="59"/>
+      <c r="C126" s="57"/>
       <c r="D126" s="50" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E126" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F126" s="26" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G126" s="24"/>
     </row>
@@ -4217,16 +4211,16 @@
       </c>
       <c r="B127" s="14"/>
       <c r="C127" s="56" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D127" s="54" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E127" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F127" s="13" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G127" s="10"/>
     </row>
@@ -4234,18 +4228,18 @@
       <c r="A128" s="9">
         <v>123</v>
       </c>
-      <c r="B128" s="57"/>
-      <c r="C128" s="59" t="s">
-        <v>299</v>
+      <c r="B128" s="58"/>
+      <c r="C128" s="57" t="s">
+        <v>298</v>
       </c>
       <c r="D128" s="51" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="E128" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F128" s="46" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="G128" s="21"/>
     </row>
@@ -4253,16 +4247,16 @@
       <c r="A129" s="9">
         <v>124</v>
       </c>
-      <c r="B129" s="58"/>
-      <c r="C129" s="59"/>
+      <c r="B129" s="59"/>
+      <c r="C129" s="57"/>
       <c r="D129" s="50" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E129" s="22" t="s">
         <v>37</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G129" s="24"/>
     </row>
@@ -4272,16 +4266,16 @@
       </c>
       <c r="B130" s="14"/>
       <c r="C130" s="56" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D130" s="54" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E130" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F130" s="13" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G130" s="10"/>
     </row>
@@ -4291,16 +4285,16 @@
       </c>
       <c r="B131" s="14"/>
       <c r="C131" s="56" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D131" s="54" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E131" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F131" s="13" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G131" s="10"/>
     </row>
@@ -4308,18 +4302,18 @@
       <c r="A132" s="9">
         <v>127</v>
       </c>
-      <c r="B132" s="57"/>
-      <c r="C132" s="59" t="s">
-        <v>302</v>
+      <c r="B132" s="58"/>
+      <c r="C132" s="57" t="s">
+        <v>301</v>
       </c>
       <c r="D132" s="51" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E132" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F132" s="45" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G132" s="21"/>
     </row>
@@ -4327,16 +4321,16 @@
       <c r="A133" s="9">
         <v>128</v>
       </c>
-      <c r="B133" s="58"/>
-      <c r="C133" s="59"/>
+      <c r="B133" s="59"/>
+      <c r="C133" s="57"/>
       <c r="D133" s="50" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="E133" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F133" s="26" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G133" s="24"/>
     </row>
@@ -4344,18 +4338,18 @@
       <c r="A134" s="9">
         <v>129</v>
       </c>
-      <c r="B134" s="57"/>
-      <c r="C134" s="59" t="s">
-        <v>303</v>
+      <c r="B134" s="58"/>
+      <c r="C134" s="57" t="s">
+        <v>302</v>
       </c>
       <c r="D134" s="51" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E134" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F134" s="45" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G134" s="21"/>
     </row>
@@ -4363,16 +4357,16 @@
       <c r="A135" s="9">
         <v>130</v>
       </c>
-      <c r="B135" s="58"/>
-      <c r="C135" s="59"/>
+      <c r="B135" s="59"/>
+      <c r="C135" s="57"/>
       <c r="D135" s="50" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E135" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F135" s="26" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="G135" s="24"/>
     </row>
@@ -4382,16 +4376,16 @@
       </c>
       <c r="B136" s="14"/>
       <c r="C136" s="56" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D136" s="54" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E136" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F136" s="13" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="G136" s="10"/>
     </row>
@@ -4399,18 +4393,18 @@
       <c r="A137" s="9">
         <v>132</v>
       </c>
-      <c r="B137" s="57"/>
-      <c r="C137" s="59" t="s">
-        <v>305</v>
+      <c r="B137" s="58"/>
+      <c r="C137" s="57" t="s">
+        <v>304</v>
       </c>
       <c r="D137" s="51" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E137" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F137" s="45" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="G137" s="21"/>
     </row>
@@ -4418,16 +4412,16 @@
       <c r="A138" s="9">
         <v>133</v>
       </c>
-      <c r="B138" s="58"/>
-      <c r="C138" s="59"/>
+      <c r="B138" s="59"/>
+      <c r="C138" s="57"/>
       <c r="D138" s="50" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E138" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F138" s="26" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="G138" s="24"/>
     </row>
@@ -4435,18 +4429,18 @@
       <c r="A139" s="9">
         <v>134</v>
       </c>
-      <c r="B139" s="57"/>
-      <c r="C139" s="64" t="s">
-        <v>306</v>
+      <c r="B139" s="58"/>
+      <c r="C139" s="60" t="s">
+        <v>305</v>
       </c>
       <c r="D139" s="51" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E139" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F139" s="45" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G139" s="21"/>
     </row>
@@ -4454,16 +4448,16 @@
       <c r="A140" s="9">
         <v>135</v>
       </c>
-      <c r="B140" s="58"/>
-      <c r="C140" s="64"/>
+      <c r="B140" s="59"/>
+      <c r="C140" s="60"/>
       <c r="D140" s="50" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E140" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F140" s="26" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="G140" s="24"/>
     </row>
@@ -4476,13 +4470,13 @@
         <v>9</v>
       </c>
       <c r="D141" s="54" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E141" s="11" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F141" s="13" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G141" s="10"/>
     </row>
@@ -4490,18 +4484,18 @@
       <c r="A142" s="9">
         <v>137</v>
       </c>
-      <c r="B142" s="57"/>
-      <c r="C142" s="59" t="s">
-        <v>307</v>
+      <c r="B142" s="58"/>
+      <c r="C142" s="57" t="s">
+        <v>306</v>
       </c>
       <c r="D142" s="51" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E142" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F142" s="45" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="G142" s="21"/>
     </row>
@@ -4509,16 +4503,16 @@
       <c r="A143" s="9">
         <v>138</v>
       </c>
-      <c r="B143" s="58"/>
-      <c r="C143" s="59"/>
+      <c r="B143" s="59"/>
+      <c r="C143" s="57"/>
       <c r="D143" s="50" t="s">
+        <v>345</v>
+      </c>
+      <c r="E143" s="22" t="s">
+        <v>310</v>
+      </c>
+      <c r="F143" s="47" t="s">
         <v>346</v>
-      </c>
-      <c r="E143" s="22" t="s">
-        <v>311</v>
-      </c>
-      <c r="F143" s="47" t="s">
-        <v>347</v>
       </c>
       <c r="G143" s="24"/>
     </row>
@@ -4526,18 +4520,18 @@
       <c r="A144" s="9">
         <v>139</v>
       </c>
-      <c r="B144" s="57"/>
-      <c r="C144" s="59" t="s">
-        <v>308</v>
+      <c r="B144" s="58"/>
+      <c r="C144" s="57" t="s">
+        <v>307</v>
       </c>
       <c r="D144" s="51" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E144" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F144" s="45" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="G144" s="21"/>
     </row>
@@ -4545,16 +4539,16 @@
       <c r="A145" s="9">
         <v>140</v>
       </c>
-      <c r="B145" s="58"/>
-      <c r="C145" s="59"/>
+      <c r="B145" s="59"/>
+      <c r="C145" s="57"/>
       <c r="D145" s="50" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E145" s="22" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F145" s="26" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="G145" s="24"/>
     </row>
@@ -4576,115 +4570,6 @@
     </row>
   </sheetData>
   <mergeCells count="133">
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="C24:C25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="B18:B19"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C38:C39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C34:C35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C52:C53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C42:C43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C44:C45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C60:C61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C62:C63"/>
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="C64:C65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="C54:C55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C56:C57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C58:C59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="C74:C75"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="C77:C78"/>
-    <mergeCell ref="C66:C67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="C68:C69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="B70:B71"/>
-    <mergeCell ref="B85:B86"/>
-    <mergeCell ref="C85:C86"/>
-    <mergeCell ref="B87:B88"/>
-    <mergeCell ref="C87:C88"/>
-    <mergeCell ref="B89:B90"/>
-    <mergeCell ref="C89:C90"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C79:C80"/>
-    <mergeCell ref="B81:B82"/>
-    <mergeCell ref="C81:C82"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:C84"/>
-    <mergeCell ref="B105:B106"/>
-    <mergeCell ref="C105:C106"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="C98:C99"/>
-    <mergeCell ref="B100:B101"/>
-    <mergeCell ref="C100:C101"/>
-    <mergeCell ref="B103:B104"/>
-    <mergeCell ref="C103:C104"/>
-    <mergeCell ref="B92:B93"/>
-    <mergeCell ref="C92:C93"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:C95"/>
-    <mergeCell ref="B96:B97"/>
-    <mergeCell ref="C96:C97"/>
-    <mergeCell ref="C114:C115"/>
-    <mergeCell ref="B117:B118"/>
-    <mergeCell ref="C117:C118"/>
-    <mergeCell ref="B119:B120"/>
-    <mergeCell ref="C119:C120"/>
-    <mergeCell ref="B107:B108"/>
-    <mergeCell ref="C107:C108"/>
-    <mergeCell ref="B109:B110"/>
-    <mergeCell ref="C109:C110"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="C112:C113"/>
     <mergeCell ref="B144:B145"/>
     <mergeCell ref="C144:C145"/>
     <mergeCell ref="A1:C1"/>
@@ -4709,6 +4594,115 @@
     <mergeCell ref="B125:B126"/>
     <mergeCell ref="C125:C126"/>
     <mergeCell ref="B114:B115"/>
+    <mergeCell ref="C114:C115"/>
+    <mergeCell ref="B117:B118"/>
+    <mergeCell ref="C117:C118"/>
+    <mergeCell ref="B119:B120"/>
+    <mergeCell ref="C119:C120"/>
+    <mergeCell ref="B107:B108"/>
+    <mergeCell ref="C107:C108"/>
+    <mergeCell ref="B109:B110"/>
+    <mergeCell ref="C109:C110"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="C112:C113"/>
+    <mergeCell ref="B105:B106"/>
+    <mergeCell ref="C105:C106"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="C98:C99"/>
+    <mergeCell ref="B100:B101"/>
+    <mergeCell ref="C100:C101"/>
+    <mergeCell ref="B103:B104"/>
+    <mergeCell ref="C103:C104"/>
+    <mergeCell ref="B92:B93"/>
+    <mergeCell ref="C92:C93"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:C95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="C96:C97"/>
+    <mergeCell ref="B85:B86"/>
+    <mergeCell ref="C85:C86"/>
+    <mergeCell ref="B87:B88"/>
+    <mergeCell ref="C87:C88"/>
+    <mergeCell ref="B89:B90"/>
+    <mergeCell ref="C89:C90"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C79:C80"/>
+    <mergeCell ref="B81:B82"/>
+    <mergeCell ref="C81:C82"/>
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:C84"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="C77:C78"/>
+    <mergeCell ref="C66:C67"/>
+    <mergeCell ref="B66:B67"/>
+    <mergeCell ref="C68:C69"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="B70:B71"/>
+    <mergeCell ref="C60:C61"/>
+    <mergeCell ref="B60:B61"/>
+    <mergeCell ref="C62:C63"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="C64:C65"/>
+    <mergeCell ref="B64:B65"/>
+    <mergeCell ref="C54:C55"/>
+    <mergeCell ref="B54:B55"/>
+    <mergeCell ref="C56:C57"/>
+    <mergeCell ref="B56:B57"/>
+    <mergeCell ref="C58:C59"/>
+    <mergeCell ref="B58:B59"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="B48:B49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="B50:B51"/>
+    <mergeCell ref="C52:C53"/>
+    <mergeCell ref="B52:B53"/>
+    <mergeCell ref="C42:C43"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="C44:C45"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C38:C39"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="B30:B31"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C24:C25"/>
+    <mergeCell ref="B24:B25"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="B20:B21"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="C10:C11"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0.35433070866141736" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
